--- a/thaco/color/Golden/1_MID_Office.xlsx
+++ b/thaco/color/Golden/1_MID_Office.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/color/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EE05797-31D2-1C4B-8D11-3DC069F9B4AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B04D4C37-9CB5-7A49-B31E-E41E954AF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38440" yWindow="500" windowWidth="38360" windowHeight="20700" tabRatio="761" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5061,7 +5061,7 @@
     <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="74">
+  <fonts count="77">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5465,23 +5465,6 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="7.5"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="7"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="7.5"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -5509,8 +5492,53 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
+      <i/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.5"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
       <sz val="7.5"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -5822,7 +5850,7 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="485">
+  <cellXfs count="476">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -6611,12 +6639,6 @@
     <xf numFmtId="165" fontId="26" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -6636,7 +6658,7 @@
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="57" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -6645,7 +6667,7 @@
     </xf>
     <xf numFmtId="165" fontId="57" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="165" fontId="57" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="57" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -6654,7 +6676,7 @@
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="58" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -6677,7 +6699,7 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -6687,12 +6709,6 @@
     <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6723,14 +6739,26 @@
     <xf numFmtId="164" fontId="15" fillId="5" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="29" fillId="3" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="3" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="15" fillId="5" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="74" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6843,10 +6871,6 @@
     <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="29" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="10" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6953,26 +6977,11 @@
     <xf numFmtId="165" fontId="4" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="67" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="68" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="72" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="72" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="26" fillId="6" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6986,34 +6995,28 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="26" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="76" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="3" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="55" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="26" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="75" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="73" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="71" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="15" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7030,33 +7033,35 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="72" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="26" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="67" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="75" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="63" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="73" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="66" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="70" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="15" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -8385,7 +8390,7 @@
       <c r="AW8" s="359" t="s">
         <v>23</v>
       </c>
-      <c r="AX8" s="393" t="s">
+      <c r="AX8" s="391" t="s">
         <v>24</v>
       </c>
       <c r="AY8" s="387" t="s">
@@ -8409,14 +8414,14 @@
       <c r="BO8" s="379"/>
       <c r="BP8" s="379"/>
       <c r="BQ8" s="385"/>
-      <c r="BR8" s="394" t="s">
+      <c r="BR8" s="392" t="s">
         <v>26</v>
       </c>
       <c r="BS8" s="373"/>
       <c r="BT8" s="335" t="s">
         <v>27</v>
       </c>
-      <c r="BU8" s="390" t="s">
+      <c r="BU8" s="388" t="s">
         <v>28</v>
       </c>
       <c r="BV8" s="3"/>
@@ -8429,13 +8434,13 @@
       <c r="BY8" s="364"/>
       <c r="BZ8" s="364"/>
       <c r="CA8" s="365"/>
-      <c r="CB8" s="395" t="s">
+      <c r="CB8" s="393" t="s">
         <v>31</v>
       </c>
       <c r="CC8" s="356" t="s">
         <v>32</v>
       </c>
-      <c r="CD8" s="388" t="s">
+      <c r="CD8" s="356" t="s">
         <v>33</v>
       </c>
       <c r="CH8" s="150"/>
@@ -8528,10 +8533,10 @@
       <c r="AJ9" s="386" t="s">
         <v>58</v>
       </c>
-      <c r="AK9" s="390" t="s">
+      <c r="AK9" s="388" t="s">
         <v>59</v>
       </c>
-      <c r="AL9" s="393" t="s">
+      <c r="AL9" s="391" t="s">
         <v>60</v>
       </c>
       <c r="AM9" s="341" t="s">
@@ -8552,29 +8557,29 @@
       <c r="AV9" s="336"/>
       <c r="AW9" s="351"/>
       <c r="AX9" s="381"/>
-      <c r="AY9" s="397" t="s">
+      <c r="AY9" s="395" t="s">
         <v>25</v>
       </c>
-      <c r="AZ9" s="398"/>
-      <c r="BA9" s="398"/>
-      <c r="BB9" s="398"/>
-      <c r="BC9" s="398"/>
-      <c r="BD9" s="398"/>
-      <c r="BE9" s="398"/>
-      <c r="BF9" s="398"/>
-      <c r="BG9" s="398"/>
-      <c r="BH9" s="398"/>
-      <c r="BI9" s="398"/>
-      <c r="BJ9" s="398"/>
-      <c r="BK9" s="398"/>
-      <c r="BL9" s="399"/>
-      <c r="BM9" s="397" t="s">
+      <c r="AZ9" s="396"/>
+      <c r="BA9" s="396"/>
+      <c r="BB9" s="396"/>
+      <c r="BC9" s="396"/>
+      <c r="BD9" s="396"/>
+      <c r="BE9" s="396"/>
+      <c r="BF9" s="396"/>
+      <c r="BG9" s="396"/>
+      <c r="BH9" s="396"/>
+      <c r="BI9" s="396"/>
+      <c r="BJ9" s="396"/>
+      <c r="BK9" s="396"/>
+      <c r="BL9" s="397"/>
+      <c r="BM9" s="395" t="s">
         <v>64</v>
       </c>
-      <c r="BN9" s="398"/>
-      <c r="BO9" s="398"/>
-      <c r="BP9" s="398"/>
-      <c r="BQ9" s="399"/>
+      <c r="BN9" s="396"/>
+      <c r="BO9" s="396"/>
+      <c r="BP9" s="396"/>
+      <c r="BQ9" s="397"/>
       <c r="BR9" s="349" t="s">
         <v>65</v>
       </c>
@@ -8582,7 +8587,7 @@
         <v>66</v>
       </c>
       <c r="BT9" s="336"/>
-      <c r="BU9" s="391"/>
+      <c r="BU9" s="389"/>
       <c r="BV9" s="3"/>
       <c r="BW9" s="339"/>
       <c r="BX9" s="366"/>
@@ -8591,7 +8596,7 @@
       <c r="CA9" s="368"/>
       <c r="CB9" s="336"/>
       <c r="CC9" s="357"/>
-      <c r="CD9" s="351"/>
+      <c r="CD9" s="357"/>
       <c r="CH9" s="150"/>
       <c r="CI9" s="150"/>
     </row>
@@ -8632,7 +8637,7 @@
       <c r="AH10" s="336"/>
       <c r="AI10" s="336"/>
       <c r="AJ10" s="381"/>
-      <c r="AK10" s="391"/>
+      <c r="AK10" s="389"/>
       <c r="AL10" s="381"/>
       <c r="AM10" s="336"/>
       <c r="AN10" s="336"/>
@@ -8706,7 +8711,7 @@
       <c r="BR10" s="347"/>
       <c r="BS10" s="347"/>
       <c r="BT10" s="336"/>
-      <c r="BU10" s="391"/>
+      <c r="BU10" s="389"/>
       <c r="BV10" s="3"/>
       <c r="BW10" s="339"/>
       <c r="BX10" s="369"/>
@@ -8715,7 +8720,7 @@
       <c r="CA10" s="371"/>
       <c r="CB10" s="336"/>
       <c r="CC10" s="357"/>
-      <c r="CD10" s="351"/>
+      <c r="CD10" s="357"/>
       <c r="CE10" s="228" t="s">
         <v>3</v>
       </c>
@@ -8763,7 +8768,7 @@
       <c r="AH11" s="337"/>
       <c r="AI11" s="337"/>
       <c r="AJ11" s="382"/>
-      <c r="AK11" s="392"/>
+      <c r="AK11" s="390"/>
       <c r="AL11" s="382"/>
       <c r="AM11" s="337"/>
       <c r="AN11" s="337"/>
@@ -8805,7 +8810,7 @@
       <c r="BR11" s="348"/>
       <c r="BS11" s="348"/>
       <c r="BT11" s="337"/>
-      <c r="BU11" s="392"/>
+      <c r="BU11" s="390"/>
       <c r="BV11" s="3"/>
       <c r="BW11" s="340"/>
       <c r="BX11" s="237" t="s">
@@ -8820,9 +8825,9 @@
       <c r="CA11" s="238" t="s">
         <v>94</v>
       </c>
-      <c r="CB11" s="396"/>
+      <c r="CB11" s="394"/>
       <c r="CC11" s="358"/>
-      <c r="CD11" s="389"/>
+      <c r="CD11" s="358"/>
       <c r="CE11" s="227">
         <v>26</v>
       </c>
@@ -11586,87 +11591,87 @@
       <c r="CD2" s="41"/>
     </row>
     <row r="3" spans="1:87" s="43" customFormat="1" ht="11" outlineLevel="1">
-      <c r="A3" s="433"/>
-      <c r="B3" s="421"/>
-      <c r="C3" s="421"/>
-      <c r="D3" s="421"/>
-      <c r="E3" s="421"/>
-      <c r="F3" s="421"/>
-      <c r="G3" s="421"/>
-      <c r="H3" s="421"/>
-      <c r="I3" s="421"/>
-      <c r="J3" s="421"/>
-      <c r="K3" s="421"/>
-      <c r="L3" s="421"/>
-      <c r="M3" s="421"/>
-      <c r="N3" s="421"/>
-      <c r="O3" s="421"/>
-      <c r="P3" s="421"/>
-      <c r="Q3" s="421"/>
-      <c r="R3" s="421"/>
-      <c r="S3" s="421"/>
-      <c r="T3" s="421"/>
-      <c r="U3" s="421"/>
-      <c r="V3" s="421"/>
-      <c r="W3" s="421"/>
-      <c r="X3" s="421"/>
-      <c r="Y3" s="421"/>
-      <c r="Z3" s="421"/>
-      <c r="AA3" s="421"/>
-      <c r="AB3" s="421"/>
-      <c r="AC3" s="421"/>
-      <c r="AD3" s="421"/>
-      <c r="AE3" s="421"/>
-      <c r="AF3" s="421"/>
-      <c r="AG3" s="421"/>
-      <c r="AH3" s="421"/>
-      <c r="AI3" s="421"/>
-      <c r="AJ3" s="421"/>
-      <c r="AK3" s="421"/>
-      <c r="AL3" s="421"/>
-      <c r="AM3" s="421"/>
-      <c r="AN3" s="421"/>
-      <c r="AO3" s="421"/>
-      <c r="AP3" s="421"/>
-      <c r="AQ3" s="421"/>
-      <c r="AR3" s="421"/>
-      <c r="AS3" s="421"/>
-      <c r="AT3" s="421"/>
-      <c r="AU3" s="421"/>
-      <c r="AV3" s="421"/>
-      <c r="AW3" s="421"/>
-      <c r="AX3" s="421"/>
-      <c r="AY3" s="421"/>
-      <c r="AZ3" s="421"/>
-      <c r="BA3" s="421"/>
-      <c r="BB3" s="421"/>
-      <c r="BC3" s="421"/>
-      <c r="BD3" s="421"/>
-      <c r="BE3" s="421"/>
-      <c r="BF3" s="421"/>
-      <c r="BG3" s="421"/>
-      <c r="BH3" s="421"/>
-      <c r="BI3" s="421"/>
-      <c r="BJ3" s="421"/>
-      <c r="BK3" s="421"/>
-      <c r="BL3" s="421"/>
-      <c r="BM3" s="421"/>
-      <c r="BN3" s="421"/>
-      <c r="BO3" s="421"/>
-      <c r="BP3" s="421"/>
-      <c r="BQ3" s="421"/>
-      <c r="BR3" s="421"/>
-      <c r="BS3" s="421"/>
-      <c r="BT3" s="421"/>
-      <c r="BU3" s="421"/>
-      <c r="BW3" s="420" t="s">
+      <c r="A3" s="431"/>
+      <c r="B3" s="419"/>
+      <c r="C3" s="419"/>
+      <c r="D3" s="419"/>
+      <c r="E3" s="419"/>
+      <c r="F3" s="419"/>
+      <c r="G3" s="419"/>
+      <c r="H3" s="419"/>
+      <c r="I3" s="419"/>
+      <c r="J3" s="419"/>
+      <c r="K3" s="419"/>
+      <c r="L3" s="419"/>
+      <c r="M3" s="419"/>
+      <c r="N3" s="419"/>
+      <c r="O3" s="419"/>
+      <c r="P3" s="419"/>
+      <c r="Q3" s="419"/>
+      <c r="R3" s="419"/>
+      <c r="S3" s="419"/>
+      <c r="T3" s="419"/>
+      <c r="U3" s="419"/>
+      <c r="V3" s="419"/>
+      <c r="W3" s="419"/>
+      <c r="X3" s="419"/>
+      <c r="Y3" s="419"/>
+      <c r="Z3" s="419"/>
+      <c r="AA3" s="419"/>
+      <c r="AB3" s="419"/>
+      <c r="AC3" s="419"/>
+      <c r="AD3" s="419"/>
+      <c r="AE3" s="419"/>
+      <c r="AF3" s="419"/>
+      <c r="AG3" s="419"/>
+      <c r="AH3" s="419"/>
+      <c r="AI3" s="419"/>
+      <c r="AJ3" s="419"/>
+      <c r="AK3" s="419"/>
+      <c r="AL3" s="419"/>
+      <c r="AM3" s="419"/>
+      <c r="AN3" s="419"/>
+      <c r="AO3" s="419"/>
+      <c r="AP3" s="419"/>
+      <c r="AQ3" s="419"/>
+      <c r="AR3" s="419"/>
+      <c r="AS3" s="419"/>
+      <c r="AT3" s="419"/>
+      <c r="AU3" s="419"/>
+      <c r="AV3" s="419"/>
+      <c r="AW3" s="419"/>
+      <c r="AX3" s="419"/>
+      <c r="AY3" s="419"/>
+      <c r="AZ3" s="419"/>
+      <c r="BA3" s="419"/>
+      <c r="BB3" s="419"/>
+      <c r="BC3" s="419"/>
+      <c r="BD3" s="419"/>
+      <c r="BE3" s="419"/>
+      <c r="BF3" s="419"/>
+      <c r="BG3" s="419"/>
+      <c r="BH3" s="419"/>
+      <c r="BI3" s="419"/>
+      <c r="BJ3" s="419"/>
+      <c r="BK3" s="419"/>
+      <c r="BL3" s="419"/>
+      <c r="BM3" s="419"/>
+      <c r="BN3" s="419"/>
+      <c r="BO3" s="419"/>
+      <c r="BP3" s="419"/>
+      <c r="BQ3" s="419"/>
+      <c r="BR3" s="419"/>
+      <c r="BS3" s="419"/>
+      <c r="BT3" s="419"/>
+      <c r="BU3" s="419"/>
+      <c r="BW3" s="418" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="421"/>
-      <c r="BY3" s="421"/>
-      <c r="BZ3" s="421"/>
-      <c r="CA3" s="421"/>
-      <c r="CB3" s="421"/>
+      <c r="BX3" s="419"/>
+      <c r="BY3" s="419"/>
+      <c r="BZ3" s="419"/>
+      <c r="CA3" s="419"/>
+      <c r="CB3" s="419"/>
       <c r="CC3" s="42"/>
       <c r="CD3" s="42"/>
       <c r="CE3" s="43" t="s">
@@ -11749,35 +11754,35 @@
       <c r="BS4" s="44"/>
       <c r="BT4" s="44"/>
       <c r="BU4" s="44"/>
-      <c r="BW4" s="421"/>
-      <c r="BX4" s="421"/>
-      <c r="BY4" s="421"/>
-      <c r="BZ4" s="421"/>
-      <c r="CA4" s="421"/>
-      <c r="CB4" s="421"/>
+      <c r="BW4" s="419"/>
+      <c r="BX4" s="419"/>
+      <c r="BY4" s="419"/>
+      <c r="BZ4" s="419"/>
+      <c r="CA4" s="419"/>
+      <c r="CB4" s="419"/>
       <c r="CC4" s="42"/>
       <c r="CD4" s="42"/>
     </row>
     <row r="5" spans="1:87" s="45" customFormat="1">
-      <c r="A5" s="408" t="s">
+      <c r="A5" s="406" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="419" t="s">
+      <c r="B5" s="417" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="407" t="s">
+      <c r="C5" s="405" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="414" t="s">
+      <c r="D5" s="412" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="414" t="s">
+      <c r="E5" s="412" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="407" t="s">
+      <c r="F5" s="405" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="407" t="s">
+      <c r="G5" s="405" t="s">
         <v>10</v>
       </c>
       <c r="H5" s="335" t="s">
@@ -11786,184 +11791,184 @@
       <c r="I5" s="335" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="407" t="s">
+      <c r="J5" s="405" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="412" t="s">
+      <c r="K5" s="410" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="404"/>
-      <c r="M5" s="404"/>
-      <c r="N5" s="404"/>
-      <c r="O5" s="404"/>
-      <c r="P5" s="404"/>
-      <c r="Q5" s="404"/>
-      <c r="R5" s="404"/>
-      <c r="S5" s="404"/>
-      <c r="T5" s="404"/>
-      <c r="U5" s="404"/>
-      <c r="V5" s="404"/>
-      <c r="W5" s="404"/>
-      <c r="X5" s="404"/>
-      <c r="Y5" s="407" t="s">
+      <c r="L5" s="402"/>
+      <c r="M5" s="402"/>
+      <c r="N5" s="402"/>
+      <c r="O5" s="402"/>
+      <c r="P5" s="402"/>
+      <c r="Q5" s="402"/>
+      <c r="R5" s="402"/>
+      <c r="S5" s="402"/>
+      <c r="T5" s="402"/>
+      <c r="U5" s="402"/>
+      <c r="V5" s="402"/>
+      <c r="W5" s="402"/>
+      <c r="X5" s="402"/>
+      <c r="Y5" s="405" t="s">
         <v>15</v>
       </c>
-      <c r="Z5" s="404"/>
-      <c r="AA5" s="404"/>
-      <c r="AB5" s="404"/>
-      <c r="AC5" s="404"/>
-      <c r="AD5" s="404"/>
-      <c r="AE5" s="404"/>
-      <c r="AF5" s="404"/>
-      <c r="AG5" s="404"/>
-      <c r="AH5" s="404"/>
-      <c r="AI5" s="404"/>
-      <c r="AJ5" s="404"/>
-      <c r="AK5" s="404"/>
-      <c r="AL5" s="404"/>
-      <c r="AM5" s="404"/>
-      <c r="AN5" s="404"/>
-      <c r="AO5" s="405"/>
-      <c r="AP5" s="407" t="s">
+      <c r="Z5" s="402"/>
+      <c r="AA5" s="402"/>
+      <c r="AB5" s="402"/>
+      <c r="AC5" s="402"/>
+      <c r="AD5" s="402"/>
+      <c r="AE5" s="402"/>
+      <c r="AF5" s="402"/>
+      <c r="AG5" s="402"/>
+      <c r="AH5" s="402"/>
+      <c r="AI5" s="402"/>
+      <c r="AJ5" s="402"/>
+      <c r="AK5" s="402"/>
+      <c r="AL5" s="402"/>
+      <c r="AM5" s="402"/>
+      <c r="AN5" s="402"/>
+      <c r="AO5" s="403"/>
+      <c r="AP5" s="405" t="s">
         <v>16</v>
       </c>
-      <c r="AQ5" s="407" t="s">
+      <c r="AQ5" s="405" t="s">
         <v>17</v>
       </c>
-      <c r="AR5" s="407" t="s">
+      <c r="AR5" s="405" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="407" t="s">
+      <c r="AS5" s="405" t="s">
         <v>19</v>
       </c>
-      <c r="AT5" s="407" t="s">
+      <c r="AT5" s="405" t="s">
         <v>20</v>
       </c>
-      <c r="AU5" s="407" t="s">
+      <c r="AU5" s="405" t="s">
         <v>21</v>
       </c>
-      <c r="AV5" s="407" t="s">
+      <c r="AV5" s="405" t="s">
         <v>22</v>
       </c>
-      <c r="AW5" s="407" t="s">
+      <c r="AW5" s="405" t="s">
         <v>23</v>
       </c>
-      <c r="AX5" s="407" t="s">
+      <c r="AX5" s="405" t="s">
         <v>24</v>
       </c>
-      <c r="AY5" s="403" t="s">
+      <c r="AY5" s="401" t="s">
         <v>25</v>
       </c>
-      <c r="AZ5" s="404"/>
-      <c r="BA5" s="404"/>
-      <c r="BB5" s="404"/>
-      <c r="BC5" s="404"/>
-      <c r="BD5" s="404"/>
-      <c r="BE5" s="404"/>
-      <c r="BF5" s="404"/>
-      <c r="BG5" s="404"/>
-      <c r="BH5" s="404"/>
-      <c r="BI5" s="404"/>
-      <c r="BJ5" s="404"/>
-      <c r="BK5" s="404"/>
-      <c r="BL5" s="404"/>
-      <c r="BM5" s="404"/>
-      <c r="BN5" s="404"/>
-      <c r="BO5" s="404"/>
-      <c r="BP5" s="404"/>
-      <c r="BQ5" s="405"/>
-      <c r="BR5" s="424" t="s">
+      <c r="AZ5" s="402"/>
+      <c r="BA5" s="402"/>
+      <c r="BB5" s="402"/>
+      <c r="BC5" s="402"/>
+      <c r="BD5" s="402"/>
+      <c r="BE5" s="402"/>
+      <c r="BF5" s="402"/>
+      <c r="BG5" s="402"/>
+      <c r="BH5" s="402"/>
+      <c r="BI5" s="402"/>
+      <c r="BJ5" s="402"/>
+      <c r="BK5" s="402"/>
+      <c r="BL5" s="402"/>
+      <c r="BM5" s="402"/>
+      <c r="BN5" s="402"/>
+      <c r="BO5" s="402"/>
+      <c r="BP5" s="402"/>
+      <c r="BQ5" s="403"/>
+      <c r="BR5" s="422" t="s">
         <v>26</v>
       </c>
-      <c r="BS5" s="417"/>
-      <c r="BT5" s="403" t="s">
+      <c r="BS5" s="415"/>
+      <c r="BT5" s="401" t="s">
         <v>27</v>
       </c>
-      <c r="BU5" s="435" t="s">
+      <c r="BU5" s="433" t="s">
         <v>28</v>
       </c>
-      <c r="BW5" s="436" t="s">
+      <c r="BW5" s="434" t="s">
         <v>29</v>
       </c>
-      <c r="BX5" s="425" t="s">
+      <c r="BX5" s="423" t="s">
         <v>30</v>
       </c>
-      <c r="BY5" s="426"/>
-      <c r="BZ5" s="426"/>
-      <c r="CA5" s="417"/>
-      <c r="CB5" s="437" t="s">
+      <c r="BY5" s="424"/>
+      <c r="BZ5" s="424"/>
+      <c r="CA5" s="415"/>
+      <c r="CB5" s="435" t="s">
         <v>31</v>
       </c>
-      <c r="CC5" s="422" t="s">
+      <c r="CC5" s="420" t="s">
         <v>32</v>
       </c>
-      <c r="CD5" s="422" t="s">
+      <c r="CD5" s="420" t="s">
         <v>33</v>
       </c>
       <c r="CH5" s="46"/>
       <c r="CI5" s="47"/>
     </row>
     <row r="6" spans="1:87" s="45" customFormat="1">
-      <c r="A6" s="401"/>
-      <c r="B6" s="401"/>
-      <c r="C6" s="401"/>
-      <c r="D6" s="401"/>
-      <c r="E6" s="401"/>
-      <c r="F6" s="401"/>
-      <c r="G6" s="401"/>
-      <c r="H6" s="401"/>
-      <c r="I6" s="401"/>
-      <c r="J6" s="401"/>
-      <c r="K6" s="415" t="s">
+      <c r="A6" s="399"/>
+      <c r="B6" s="399"/>
+      <c r="C6" s="399"/>
+      <c r="D6" s="399"/>
+      <c r="E6" s="399"/>
+      <c r="F6" s="399"/>
+      <c r="G6" s="399"/>
+      <c r="H6" s="399"/>
+      <c r="I6" s="399"/>
+      <c r="J6" s="399"/>
+      <c r="K6" s="413" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="415" t="s">
+      <c r="L6" s="413" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="415" t="s">
+      <c r="M6" s="413" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="415" t="s">
+      <c r="N6" s="413" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="415" t="s">
+      <c r="O6" s="413" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="415" t="s">
+      <c r="P6" s="413" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="415" t="s">
+      <c r="Q6" s="413" t="s">
         <v>40</v>
       </c>
-      <c r="R6" s="415" t="s">
+      <c r="R6" s="413" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="415" t="s">
+      <c r="S6" s="413" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="415" t="s">
+      <c r="T6" s="413" t="s">
         <v>43</v>
       </c>
-      <c r="U6" s="415" t="s">
+      <c r="U6" s="413" t="s">
         <v>44</v>
       </c>
-      <c r="V6" s="416" t="s">
+      <c r="V6" s="414" t="s">
         <v>45</v>
       </c>
-      <c r="W6" s="417"/>
-      <c r="X6" s="415" t="s">
+      <c r="W6" s="415"/>
+      <c r="X6" s="413" t="s">
         <v>46</v>
       </c>
-      <c r="Y6" s="407" t="s">
+      <c r="Y6" s="405" t="s">
         <v>47</v>
       </c>
-      <c r="Z6" s="407" t="s">
+      <c r="Z6" s="405" t="s">
         <v>48</v>
       </c>
-      <c r="AA6" s="407" t="s">
+      <c r="AA6" s="405" t="s">
         <v>49</v>
       </c>
-      <c r="AB6" s="407" t="s">
+      <c r="AB6" s="405" t="s">
         <v>50</v>
       </c>
       <c r="AC6" s="335" t="s">
@@ -11978,7 +11983,7 @@
       <c r="AF6" s="335" t="s">
         <v>54</v>
       </c>
-      <c r="AG6" s="407" t="s">
+      <c r="AG6" s="405" t="s">
         <v>55</v>
       </c>
       <c r="AH6" s="335" t="s">
@@ -11987,126 +11992,126 @@
       <c r="AI6" s="335" t="s">
         <v>57</v>
       </c>
-      <c r="AJ6" s="407" t="s">
+      <c r="AJ6" s="405" t="s">
         <v>58</v>
       </c>
-      <c r="AK6" s="409" t="s">
+      <c r="AK6" s="407" t="s">
         <v>59</v>
       </c>
-      <c r="AL6" s="407" t="s">
+      <c r="AL6" s="405" t="s">
         <v>60</v>
       </c>
-      <c r="AM6" s="407" t="s">
+      <c r="AM6" s="405" t="s">
         <v>61</v>
       </c>
-      <c r="AN6" s="413" t="s">
+      <c r="AN6" s="411" t="s">
         <v>62</v>
       </c>
-      <c r="AO6" s="407" t="s">
+      <c r="AO6" s="405" t="s">
         <v>63</v>
       </c>
-      <c r="AP6" s="401"/>
-      <c r="AQ6" s="401"/>
-      <c r="AR6" s="401"/>
-      <c r="AS6" s="401"/>
-      <c r="AT6" s="401"/>
-      <c r="AU6" s="401"/>
-      <c r="AV6" s="401"/>
-      <c r="AW6" s="401"/>
-      <c r="AX6" s="401"/>
-      <c r="AY6" s="403" t="s">
+      <c r="AP6" s="399"/>
+      <c r="AQ6" s="399"/>
+      <c r="AR6" s="399"/>
+      <c r="AS6" s="399"/>
+      <c r="AT6" s="399"/>
+      <c r="AU6" s="399"/>
+      <c r="AV6" s="399"/>
+      <c r="AW6" s="399"/>
+      <c r="AX6" s="399"/>
+      <c r="AY6" s="401" t="s">
         <v>25</v>
       </c>
-      <c r="AZ6" s="404"/>
-      <c r="BA6" s="404"/>
-      <c r="BB6" s="404"/>
-      <c r="BC6" s="404"/>
-      <c r="BD6" s="404"/>
-      <c r="BE6" s="404"/>
-      <c r="BF6" s="404"/>
-      <c r="BG6" s="404"/>
-      <c r="BH6" s="404"/>
-      <c r="BI6" s="404"/>
-      <c r="BJ6" s="404"/>
-      <c r="BK6" s="404"/>
-      <c r="BL6" s="405"/>
-      <c r="BM6" s="403" t="s">
+      <c r="AZ6" s="402"/>
+      <c r="BA6" s="402"/>
+      <c r="BB6" s="402"/>
+      <c r="BC6" s="402"/>
+      <c r="BD6" s="402"/>
+      <c r="BE6" s="402"/>
+      <c r="BF6" s="402"/>
+      <c r="BG6" s="402"/>
+      <c r="BH6" s="402"/>
+      <c r="BI6" s="402"/>
+      <c r="BJ6" s="402"/>
+      <c r="BK6" s="402"/>
+      <c r="BL6" s="403"/>
+      <c r="BM6" s="401" t="s">
         <v>64</v>
       </c>
-      <c r="BN6" s="404"/>
-      <c r="BO6" s="404"/>
-      <c r="BP6" s="404"/>
-      <c r="BQ6" s="405"/>
-      <c r="BR6" s="400" t="s">
+      <c r="BN6" s="402"/>
+      <c r="BO6" s="402"/>
+      <c r="BP6" s="402"/>
+      <c r="BQ6" s="403"/>
+      <c r="BR6" s="398" t="s">
         <v>65</v>
       </c>
-      <c r="BS6" s="400" t="s">
+      <c r="BS6" s="398" t="s">
         <v>66</v>
       </c>
-      <c r="BT6" s="401"/>
-      <c r="BU6" s="410"/>
-      <c r="BW6" s="428"/>
-      <c r="BX6" s="410"/>
-      <c r="BY6" s="427"/>
-      <c r="BZ6" s="427"/>
-      <c r="CA6" s="428"/>
-      <c r="CB6" s="401"/>
-      <c r="CC6" s="401"/>
-      <c r="CD6" s="401"/>
+      <c r="BT6" s="399"/>
+      <c r="BU6" s="408"/>
+      <c r="BW6" s="426"/>
+      <c r="BX6" s="408"/>
+      <c r="BY6" s="425"/>
+      <c r="BZ6" s="425"/>
+      <c r="CA6" s="426"/>
+      <c r="CB6" s="399"/>
+      <c r="CC6" s="399"/>
+      <c r="CD6" s="399"/>
       <c r="CH6" s="46"/>
       <c r="CI6" s="47"/>
     </row>
     <row r="7" spans="1:87" s="48" customFormat="1" ht="12">
-      <c r="A7" s="401"/>
-      <c r="B7" s="401"/>
-      <c r="C7" s="401"/>
-      <c r="D7" s="401"/>
-      <c r="E7" s="401"/>
-      <c r="F7" s="401"/>
-      <c r="G7" s="401"/>
-      <c r="H7" s="401"/>
-      <c r="I7" s="401"/>
-      <c r="J7" s="401"/>
-      <c r="K7" s="401"/>
-      <c r="L7" s="401"/>
-      <c r="M7" s="401"/>
-      <c r="N7" s="401"/>
-      <c r="O7" s="401"/>
-      <c r="P7" s="401"/>
-      <c r="Q7" s="401"/>
-      <c r="R7" s="401"/>
-      <c r="S7" s="401"/>
-      <c r="T7" s="401"/>
-      <c r="U7" s="401"/>
-      <c r="V7" s="411"/>
-      <c r="W7" s="418"/>
-      <c r="X7" s="401"/>
-      <c r="Y7" s="401"/>
-      <c r="Z7" s="401"/>
-      <c r="AA7" s="401"/>
-      <c r="AB7" s="401"/>
-      <c r="AC7" s="401"/>
-      <c r="AD7" s="401"/>
-      <c r="AE7" s="401"/>
-      <c r="AF7" s="401"/>
-      <c r="AG7" s="401"/>
-      <c r="AH7" s="401"/>
-      <c r="AI7" s="401"/>
-      <c r="AJ7" s="401"/>
-      <c r="AK7" s="410"/>
-      <c r="AL7" s="401"/>
-      <c r="AM7" s="401"/>
-      <c r="AN7" s="401"/>
-      <c r="AO7" s="401"/>
-      <c r="AP7" s="401"/>
-      <c r="AQ7" s="401"/>
-      <c r="AR7" s="401"/>
-      <c r="AS7" s="401"/>
-      <c r="AT7" s="401"/>
-      <c r="AU7" s="401"/>
-      <c r="AV7" s="401"/>
-      <c r="AW7" s="401"/>
-      <c r="AX7" s="401"/>
+      <c r="A7" s="399"/>
+      <c r="B7" s="399"/>
+      <c r="C7" s="399"/>
+      <c r="D7" s="399"/>
+      <c r="E7" s="399"/>
+      <c r="F7" s="399"/>
+      <c r="G7" s="399"/>
+      <c r="H7" s="399"/>
+      <c r="I7" s="399"/>
+      <c r="J7" s="399"/>
+      <c r="K7" s="399"/>
+      <c r="L7" s="399"/>
+      <c r="M7" s="399"/>
+      <c r="N7" s="399"/>
+      <c r="O7" s="399"/>
+      <c r="P7" s="399"/>
+      <c r="Q7" s="399"/>
+      <c r="R7" s="399"/>
+      <c r="S7" s="399"/>
+      <c r="T7" s="399"/>
+      <c r="U7" s="399"/>
+      <c r="V7" s="409"/>
+      <c r="W7" s="416"/>
+      <c r="X7" s="399"/>
+      <c r="Y7" s="399"/>
+      <c r="Z7" s="399"/>
+      <c r="AA7" s="399"/>
+      <c r="AB7" s="399"/>
+      <c r="AC7" s="399"/>
+      <c r="AD7" s="399"/>
+      <c r="AE7" s="399"/>
+      <c r="AF7" s="399"/>
+      <c r="AG7" s="399"/>
+      <c r="AH7" s="399"/>
+      <c r="AI7" s="399"/>
+      <c r="AJ7" s="399"/>
+      <c r="AK7" s="408"/>
+      <c r="AL7" s="399"/>
+      <c r="AM7" s="399"/>
+      <c r="AN7" s="399"/>
+      <c r="AO7" s="399"/>
+      <c r="AP7" s="399"/>
+      <c r="AQ7" s="399"/>
+      <c r="AR7" s="399"/>
+      <c r="AS7" s="399"/>
+      <c r="AT7" s="399"/>
+      <c r="AU7" s="399"/>
+      <c r="AV7" s="399"/>
+      <c r="AW7" s="399"/>
+      <c r="AX7" s="399"/>
       <c r="AY7" s="29" t="s">
         <v>67</v>
       </c>
@@ -12116,124 +12121,124 @@
       <c r="BA7" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="BB7" s="403" t="s">
+      <c r="BB7" s="401" t="s">
         <v>70</v>
       </c>
-      <c r="BC7" s="406" t="s">
+      <c r="BC7" s="404" t="s">
         <v>71</v>
       </c>
-      <c r="BD7" s="406" t="s">
+      <c r="BD7" s="404" t="s">
         <v>72</v>
       </c>
-      <c r="BE7" s="432" t="s">
+      <c r="BE7" s="430" t="s">
         <v>73</v>
       </c>
-      <c r="BF7" s="406" t="s">
+      <c r="BF7" s="404" t="s">
         <v>74</v>
       </c>
-      <c r="BG7" s="406" t="s">
+      <c r="BG7" s="404" t="s">
         <v>75</v>
       </c>
-      <c r="BH7" s="406" t="s">
+      <c r="BH7" s="404" t="s">
         <v>76</v>
       </c>
-      <c r="BI7" s="406" t="s">
+      <c r="BI7" s="404" t="s">
         <v>77</v>
       </c>
-      <c r="BJ7" s="406" t="s">
+      <c r="BJ7" s="404" t="s">
         <v>78</v>
       </c>
-      <c r="BK7" s="406" t="s">
+      <c r="BK7" s="404" t="s">
         <v>79</v>
       </c>
-      <c r="BL7" s="434" t="s">
+      <c r="BL7" s="432" t="s">
         <v>80</v>
       </c>
-      <c r="BM7" s="406" t="s">
+      <c r="BM7" s="404" t="s">
         <v>81</v>
       </c>
-      <c r="BN7" s="403" t="s">
+      <c r="BN7" s="401" t="s">
         <v>82</v>
       </c>
-      <c r="BO7" s="406" t="s">
+      <c r="BO7" s="404" t="s">
         <v>83</v>
       </c>
-      <c r="BP7" s="403" t="s">
+      <c r="BP7" s="401" t="s">
         <v>84</v>
       </c>
-      <c r="BQ7" s="403" t="s">
+      <c r="BQ7" s="401" t="s">
         <v>85</v>
       </c>
-      <c r="BR7" s="401"/>
-      <c r="BS7" s="401"/>
-      <c r="BT7" s="401"/>
-      <c r="BU7" s="410"/>
-      <c r="BW7" s="428"/>
-      <c r="BX7" s="429"/>
-      <c r="BY7" s="430"/>
-      <c r="BZ7" s="430"/>
-      <c r="CA7" s="431"/>
-      <c r="CB7" s="401"/>
-      <c r="CC7" s="401"/>
-      <c r="CD7" s="401"/>
+      <c r="BR7" s="399"/>
+      <c r="BS7" s="399"/>
+      <c r="BT7" s="399"/>
+      <c r="BU7" s="408"/>
+      <c r="BW7" s="426"/>
+      <c r="BX7" s="427"/>
+      <c r="BY7" s="428"/>
+      <c r="BZ7" s="428"/>
+      <c r="CA7" s="429"/>
+      <c r="CB7" s="399"/>
+      <c r="CC7" s="399"/>
+      <c r="CD7" s="399"/>
       <c r="CH7" s="46"/>
       <c r="CI7" s="47"/>
     </row>
     <row r="8" spans="1:87" s="48" customFormat="1" ht="12">
-      <c r="A8" s="402"/>
-      <c r="B8" s="402"/>
-      <c r="C8" s="402"/>
-      <c r="D8" s="402"/>
-      <c r="E8" s="402"/>
-      <c r="F8" s="402"/>
-      <c r="G8" s="402"/>
-      <c r="H8" s="402"/>
-      <c r="I8" s="402"/>
-      <c r="J8" s="402"/>
-      <c r="K8" s="402"/>
-      <c r="L8" s="402"/>
-      <c r="M8" s="402"/>
-      <c r="N8" s="402"/>
-      <c r="O8" s="402"/>
-      <c r="P8" s="402"/>
-      <c r="Q8" s="402"/>
-      <c r="R8" s="402"/>
-      <c r="S8" s="402"/>
-      <c r="T8" s="402"/>
-      <c r="U8" s="402"/>
+      <c r="A8" s="400"/>
+      <c r="B8" s="400"/>
+      <c r="C8" s="400"/>
+      <c r="D8" s="400"/>
+      <c r="E8" s="400"/>
+      <c r="F8" s="400"/>
+      <c r="G8" s="400"/>
+      <c r="H8" s="400"/>
+      <c r="I8" s="400"/>
+      <c r="J8" s="400"/>
+      <c r="K8" s="400"/>
+      <c r="L8" s="400"/>
+      <c r="M8" s="400"/>
+      <c r="N8" s="400"/>
+      <c r="O8" s="400"/>
+      <c r="P8" s="400"/>
+      <c r="Q8" s="400"/>
+      <c r="R8" s="400"/>
+      <c r="S8" s="400"/>
+      <c r="T8" s="400"/>
+      <c r="U8" s="400"/>
       <c r="V8" s="49" t="s">
         <v>86</v>
       </c>
       <c r="W8" s="49" t="s">
         <v>87</v>
       </c>
-      <c r="X8" s="402"/>
-      <c r="Y8" s="402"/>
-      <c r="Z8" s="402"/>
-      <c r="AA8" s="402"/>
-      <c r="AB8" s="402"/>
-      <c r="AC8" s="402"/>
-      <c r="AD8" s="402"/>
-      <c r="AE8" s="402"/>
-      <c r="AF8" s="402"/>
-      <c r="AG8" s="402"/>
-      <c r="AH8" s="402"/>
-      <c r="AI8" s="402"/>
-      <c r="AJ8" s="402"/>
-      <c r="AK8" s="411"/>
-      <c r="AL8" s="402"/>
-      <c r="AM8" s="402"/>
-      <c r="AN8" s="402"/>
-      <c r="AO8" s="402"/>
-      <c r="AP8" s="402"/>
-      <c r="AQ8" s="402"/>
-      <c r="AR8" s="402"/>
-      <c r="AS8" s="402"/>
-      <c r="AT8" s="402"/>
-      <c r="AU8" s="402"/>
-      <c r="AV8" s="402"/>
-      <c r="AW8" s="402"/>
-      <c r="AX8" s="402"/>
+      <c r="X8" s="400"/>
+      <c r="Y8" s="400"/>
+      <c r="Z8" s="400"/>
+      <c r="AA8" s="400"/>
+      <c r="AB8" s="400"/>
+      <c r="AC8" s="400"/>
+      <c r="AD8" s="400"/>
+      <c r="AE8" s="400"/>
+      <c r="AF8" s="400"/>
+      <c r="AG8" s="400"/>
+      <c r="AH8" s="400"/>
+      <c r="AI8" s="400"/>
+      <c r="AJ8" s="400"/>
+      <c r="AK8" s="409"/>
+      <c r="AL8" s="400"/>
+      <c r="AM8" s="400"/>
+      <c r="AN8" s="400"/>
+      <c r="AO8" s="400"/>
+      <c r="AP8" s="400"/>
+      <c r="AQ8" s="400"/>
+      <c r="AR8" s="400"/>
+      <c r="AS8" s="400"/>
+      <c r="AT8" s="400"/>
+      <c r="AU8" s="400"/>
+      <c r="AV8" s="400"/>
+      <c r="AW8" s="400"/>
+      <c r="AX8" s="400"/>
       <c r="AY8" s="30" t="s">
         <v>88</v>
       </c>
@@ -12243,27 +12248,27 @@
       <c r="BA8" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="BB8" s="402"/>
-      <c r="BC8" s="402"/>
-      <c r="BD8" s="402"/>
-      <c r="BE8" s="402"/>
-      <c r="BF8" s="402"/>
-      <c r="BG8" s="402"/>
-      <c r="BH8" s="402"/>
-      <c r="BI8" s="402"/>
-      <c r="BJ8" s="402"/>
-      <c r="BK8" s="402"/>
-      <c r="BL8" s="402"/>
-      <c r="BM8" s="402"/>
-      <c r="BN8" s="402"/>
-      <c r="BO8" s="402"/>
-      <c r="BP8" s="402"/>
-      <c r="BQ8" s="402"/>
-      <c r="BR8" s="402"/>
-      <c r="BS8" s="402"/>
-      <c r="BT8" s="402"/>
-      <c r="BU8" s="411"/>
-      <c r="BW8" s="431"/>
+      <c r="BB8" s="400"/>
+      <c r="BC8" s="400"/>
+      <c r="BD8" s="400"/>
+      <c r="BE8" s="400"/>
+      <c r="BF8" s="400"/>
+      <c r="BG8" s="400"/>
+      <c r="BH8" s="400"/>
+      <c r="BI8" s="400"/>
+      <c r="BJ8" s="400"/>
+      <c r="BK8" s="400"/>
+      <c r="BL8" s="400"/>
+      <c r="BM8" s="400"/>
+      <c r="BN8" s="400"/>
+      <c r="BO8" s="400"/>
+      <c r="BP8" s="400"/>
+      <c r="BQ8" s="400"/>
+      <c r="BR8" s="400"/>
+      <c r="BS8" s="400"/>
+      <c r="BT8" s="400"/>
+      <c r="BU8" s="409"/>
+      <c r="BW8" s="429"/>
       <c r="BX8" s="23" t="s">
         <v>91</v>
       </c>
@@ -12276,9 +12281,9 @@
       <c r="CA8" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="CB8" s="423"/>
-      <c r="CC8" s="423"/>
-      <c r="CD8" s="423"/>
+      <c r="CB8" s="421"/>
+      <c r="CC8" s="421"/>
+      <c r="CD8" s="421"/>
       <c r="CE8" s="45"/>
       <c r="CF8" s="50"/>
       <c r="CH8" s="46"/>
@@ -14849,16 +14854,16 @@
   <dimension ref="A1:CG26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" outlineLevelRow="1" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="5.5" style="311" customWidth="1"/>
-    <col min="2" max="2" width="8.5" style="312" customWidth="1"/>
-    <col min="3" max="3" width="18.1640625" style="313" customWidth="1"/>
-    <col min="4" max="4" width="5.5" style="255" bestFit="1" customWidth="1" outlineLevel="1"/>
-    <col min="5" max="5" width="5.5" style="255" customWidth="1" outlineLevel="1"/>
+    <col min="1" max="1" width="5.5" style="309" customWidth="1"/>
+    <col min="2" max="2" width="8.5" style="310" customWidth="1"/>
+    <col min="3" max="3" width="18.1640625" style="311" customWidth="1"/>
+    <col min="4" max="4" width="19.6640625" style="255" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="5" width="19.83203125" style="255" customWidth="1" outlineLevel="1"/>
     <col min="6" max="6" width="5.5" style="256" bestFit="1" customWidth="1" outlineLevel="1"/>
     <col min="7" max="7" width="13.6640625" style="258" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.5" style="258" customWidth="1"/>
-    <col min="9" max="9" width="12.5" style="316" customWidth="1"/>
-    <col min="10" max="10" width="7.5" style="316" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="12.5" style="314" customWidth="1"/>
+    <col min="10" max="10" width="7.5" style="314" customWidth="1" outlineLevel="1"/>
     <col min="11" max="24" width="7.1640625" style="257" customWidth="1"/>
     <col min="25" max="47" width="12.33203125" style="258" customWidth="1"/>
     <col min="48" max="49" width="13" style="258" customWidth="1"/>
@@ -14867,14 +14872,14 @@
     <col min="54" max="71" width="10.5" style="258" customWidth="1"/>
     <col min="72" max="72" width="12.5" style="258" customWidth="1"/>
     <col min="73" max="77" width="12.6640625" style="258" customWidth="1" outlineLevel="1"/>
-    <col min="78" max="78" width="12.6640625" style="317" customWidth="1" outlineLevel="1"/>
-    <col min="79" max="80" width="10.6640625" style="317" customWidth="1" outlineLevel="1"/>
-    <col min="81" max="81" width="19.5" style="318" customWidth="1"/>
-    <col min="82" max="82" width="12.33203125" style="318" customWidth="1"/>
-    <col min="83" max="83" width="12.5" style="318" customWidth="1"/>
-    <col min="84" max="84" width="11.6640625" style="318" customWidth="1"/>
-    <col min="85" max="85" width="9.1640625" style="318" customWidth="1"/>
-    <col min="86" max="16384" width="9.1640625" style="318"/>
+    <col min="78" max="78" width="12.6640625" style="315" customWidth="1" outlineLevel="1"/>
+    <col min="79" max="80" width="10.6640625" style="315" customWidth="1" outlineLevel="1"/>
+    <col min="81" max="81" width="19.5" style="316" customWidth="1"/>
+    <col min="82" max="82" width="12.33203125" style="316" customWidth="1"/>
+    <col min="83" max="83" width="12.5" style="316" customWidth="1"/>
+    <col min="84" max="84" width="11.6640625" style="316" customWidth="1"/>
+    <col min="85" max="85" width="9.1640625" style="316" customWidth="1"/>
+    <col min="86" max="16384" width="9.1640625" style="316"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:85" s="239" customFormat="1" ht="23.25" customHeight="1" outlineLevel="1">
@@ -15039,86 +15044,86 @@
       <c r="CB2" s="268"/>
     </row>
     <row r="3" spans="1:85" s="240" customFormat="1" ht="24" customHeight="1" outlineLevel="1">
-      <c r="A3" s="473"/>
-      <c r="B3" s="472"/>
-      <c r="C3" s="472"/>
-      <c r="D3" s="472"/>
-      <c r="E3" s="472"/>
-      <c r="F3" s="472"/>
-      <c r="G3" s="472"/>
-      <c r="H3" s="472"/>
-      <c r="I3" s="472"/>
-      <c r="J3" s="472"/>
-      <c r="K3" s="472"/>
-      <c r="L3" s="472"/>
-      <c r="M3" s="472"/>
-      <c r="N3" s="472"/>
-      <c r="O3" s="472"/>
-      <c r="P3" s="472"/>
-      <c r="Q3" s="472"/>
-      <c r="R3" s="472"/>
-      <c r="S3" s="472"/>
-      <c r="T3" s="472"/>
-      <c r="U3" s="472"/>
-      <c r="V3" s="472"/>
-      <c r="W3" s="472"/>
-      <c r="X3" s="472"/>
-      <c r="Y3" s="472"/>
-      <c r="Z3" s="472"/>
-      <c r="AA3" s="472"/>
-      <c r="AB3" s="472"/>
-      <c r="AC3" s="472"/>
-      <c r="AD3" s="472"/>
-      <c r="AE3" s="472"/>
-      <c r="AF3" s="472"/>
-      <c r="AG3" s="472"/>
-      <c r="AH3" s="472"/>
-      <c r="AI3" s="472"/>
-      <c r="AJ3" s="472"/>
-      <c r="AK3" s="472"/>
-      <c r="AL3" s="472"/>
-      <c r="AM3" s="472"/>
-      <c r="AN3" s="472"/>
-      <c r="AO3" s="472"/>
-      <c r="AP3" s="472"/>
-      <c r="AQ3" s="472"/>
-      <c r="AR3" s="472"/>
-      <c r="AS3" s="472"/>
-      <c r="AT3" s="472"/>
-      <c r="AU3" s="472"/>
-      <c r="AV3" s="472"/>
-      <c r="AW3" s="472"/>
-      <c r="AX3" s="472"/>
-      <c r="AY3" s="472"/>
-      <c r="AZ3" s="472"/>
-      <c r="BA3" s="472"/>
-      <c r="BB3" s="472"/>
-      <c r="BC3" s="472"/>
-      <c r="BD3" s="472"/>
-      <c r="BE3" s="472"/>
-      <c r="BF3" s="472"/>
-      <c r="BG3" s="472"/>
-      <c r="BH3" s="472"/>
-      <c r="BI3" s="472"/>
-      <c r="BJ3" s="472"/>
-      <c r="BK3" s="472"/>
-      <c r="BL3" s="472"/>
-      <c r="BM3" s="472"/>
-      <c r="BN3" s="472"/>
-      <c r="BO3" s="472"/>
-      <c r="BP3" s="472"/>
-      <c r="BQ3" s="472"/>
-      <c r="BR3" s="472"/>
-      <c r="BS3" s="472"/>
-      <c r="BT3" s="472"/>
-      <c r="BU3" s="471" t="s">
+      <c r="A3" s="463"/>
+      <c r="B3" s="461"/>
+      <c r="C3" s="461"/>
+      <c r="D3" s="461"/>
+      <c r="E3" s="461"/>
+      <c r="F3" s="461"/>
+      <c r="G3" s="461"/>
+      <c r="H3" s="461"/>
+      <c r="I3" s="461"/>
+      <c r="J3" s="461"/>
+      <c r="K3" s="461"/>
+      <c r="L3" s="461"/>
+      <c r="M3" s="461"/>
+      <c r="N3" s="461"/>
+      <c r="O3" s="461"/>
+      <c r="P3" s="461"/>
+      <c r="Q3" s="461"/>
+      <c r="R3" s="461"/>
+      <c r="S3" s="461"/>
+      <c r="T3" s="461"/>
+      <c r="U3" s="461"/>
+      <c r="V3" s="461"/>
+      <c r="W3" s="461"/>
+      <c r="X3" s="461"/>
+      <c r="Y3" s="461"/>
+      <c r="Z3" s="461"/>
+      <c r="AA3" s="461"/>
+      <c r="AB3" s="461"/>
+      <c r="AC3" s="461"/>
+      <c r="AD3" s="461"/>
+      <c r="AE3" s="461"/>
+      <c r="AF3" s="461"/>
+      <c r="AG3" s="461"/>
+      <c r="AH3" s="461"/>
+      <c r="AI3" s="461"/>
+      <c r="AJ3" s="461"/>
+      <c r="AK3" s="461"/>
+      <c r="AL3" s="461"/>
+      <c r="AM3" s="461"/>
+      <c r="AN3" s="461"/>
+      <c r="AO3" s="461"/>
+      <c r="AP3" s="461"/>
+      <c r="AQ3" s="461"/>
+      <c r="AR3" s="461"/>
+      <c r="AS3" s="461"/>
+      <c r="AT3" s="461"/>
+      <c r="AU3" s="461"/>
+      <c r="AV3" s="461"/>
+      <c r="AW3" s="461"/>
+      <c r="AX3" s="461"/>
+      <c r="AY3" s="461"/>
+      <c r="AZ3" s="461"/>
+      <c r="BA3" s="461"/>
+      <c r="BB3" s="461"/>
+      <c r="BC3" s="461"/>
+      <c r="BD3" s="461"/>
+      <c r="BE3" s="461"/>
+      <c r="BF3" s="461"/>
+      <c r="BG3" s="461"/>
+      <c r="BH3" s="461"/>
+      <c r="BI3" s="461"/>
+      <c r="BJ3" s="461"/>
+      <c r="BK3" s="461"/>
+      <c r="BL3" s="461"/>
+      <c r="BM3" s="461"/>
+      <c r="BN3" s="461"/>
+      <c r="BO3" s="461"/>
+      <c r="BP3" s="461"/>
+      <c r="BQ3" s="461"/>
+      <c r="BR3" s="461"/>
+      <c r="BS3" s="461"/>
+      <c r="BT3" s="461"/>
+      <c r="BU3" s="460" t="s">
         <v>2</v>
       </c>
-      <c r="BV3" s="472"/>
-      <c r="BW3" s="472"/>
-      <c r="BX3" s="472"/>
-      <c r="BY3" s="472"/>
-      <c r="BZ3" s="472"/>
+      <c r="BV3" s="461"/>
+      <c r="BW3" s="461"/>
+      <c r="BX3" s="461"/>
+      <c r="BY3" s="461"/>
+      <c r="BZ3" s="461"/>
       <c r="CA3" s="270"/>
       <c r="CB3" s="270"/>
     </row>
@@ -15194,12 +15199,12 @@
       <c r="BR4" s="271"/>
       <c r="BS4" s="271"/>
       <c r="BT4" s="271"/>
-      <c r="BU4" s="472"/>
-      <c r="BV4" s="472"/>
-      <c r="BW4" s="472"/>
-      <c r="BX4" s="472"/>
-      <c r="BY4" s="472"/>
-      <c r="BZ4" s="472"/>
+      <c r="BU4" s="461"/>
+      <c r="BV4" s="461"/>
+      <c r="BW4" s="461"/>
+      <c r="BX4" s="461"/>
+      <c r="BY4" s="461"/>
+      <c r="BZ4" s="461"/>
       <c r="CA4" s="270"/>
       <c r="CB4" s="270"/>
     </row>
@@ -15275,12 +15280,12 @@
       <c r="BR5" s="271"/>
       <c r="BS5" s="271"/>
       <c r="BT5" s="271"/>
-      <c r="BU5" s="472"/>
-      <c r="BV5" s="472"/>
-      <c r="BW5" s="472"/>
-      <c r="BX5" s="472"/>
-      <c r="BY5" s="472"/>
-      <c r="BZ5" s="472"/>
+      <c r="BU5" s="461"/>
+      <c r="BV5" s="461"/>
+      <c r="BW5" s="461"/>
+      <c r="BX5" s="461"/>
+      <c r="BY5" s="461"/>
+      <c r="BZ5" s="461"/>
       <c r="CA5" s="270"/>
       <c r="CB5" s="270"/>
     </row>
@@ -15356,12 +15361,12 @@
       <c r="BR6" s="273"/>
       <c r="BS6" s="273"/>
       <c r="BT6" s="273"/>
-      <c r="BU6" s="472"/>
-      <c r="BV6" s="472"/>
-      <c r="BW6" s="472"/>
-      <c r="BX6" s="472"/>
-      <c r="BY6" s="472"/>
-      <c r="BZ6" s="472"/>
+      <c r="BU6" s="461"/>
+      <c r="BV6" s="461"/>
+      <c r="BW6" s="461"/>
+      <c r="BX6" s="461"/>
+      <c r="BY6" s="461"/>
+      <c r="BZ6" s="461"/>
       <c r="CA6" s="270"/>
       <c r="CB6" s="270"/>
     </row>
@@ -15446,480 +15451,480 @@
       <c r="CA7" s="283"/>
       <c r="CB7" s="283"/>
     </row>
-    <row r="8" spans="1:85" s="284" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A8" s="445" t="s">
+    <row r="8" spans="1:85" s="330" customFormat="1" ht="19.25" customHeight="1">
+      <c r="A8" s="436" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="474" t="s">
+      <c r="B8" s="464" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="455" t="s">
+      <c r="C8" s="411" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="460" t="s">
+      <c r="D8" s="450" t="s">
         <v>141</v>
       </c>
-      <c r="E8" s="460" t="s">
+      <c r="E8" s="450" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="462" t="s">
+      <c r="F8" s="472" t="s">
         <v>142</v>
       </c>
-      <c r="G8" s="350" t="s">
+      <c r="G8" s="380" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="465" t="s">
+      <c r="H8" s="454" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="465" t="s">
+      <c r="I8" s="454" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="350" t="s">
+      <c r="J8" s="380" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="467" t="s">
+      <c r="K8" s="456" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="468"/>
-      <c r="M8" s="468"/>
-      <c r="N8" s="468"/>
-      <c r="O8" s="468"/>
-      <c r="P8" s="468"/>
-      <c r="Q8" s="468"/>
-      <c r="R8" s="468"/>
-      <c r="S8" s="468"/>
-      <c r="T8" s="468"/>
-      <c r="U8" s="468"/>
-      <c r="V8" s="468"/>
-      <c r="W8" s="468"/>
-      <c r="X8" s="468"/>
-      <c r="Y8" s="482" t="s">
+      <c r="L8" s="457"/>
+      <c r="M8" s="457"/>
+      <c r="N8" s="457"/>
+      <c r="O8" s="457"/>
+      <c r="P8" s="457"/>
+      <c r="Q8" s="457"/>
+      <c r="R8" s="457"/>
+      <c r="S8" s="457"/>
+      <c r="T8" s="457"/>
+      <c r="U8" s="457"/>
+      <c r="V8" s="457"/>
+      <c r="W8" s="457"/>
+      <c r="X8" s="457"/>
+      <c r="Y8" s="473" t="s">
         <v>15</v>
       </c>
-      <c r="Z8" s="468"/>
-      <c r="AA8" s="468"/>
-      <c r="AB8" s="468"/>
-      <c r="AC8" s="468"/>
-      <c r="AD8" s="468"/>
-      <c r="AE8" s="468"/>
-      <c r="AF8" s="468"/>
-      <c r="AG8" s="468"/>
-      <c r="AH8" s="468"/>
-      <c r="AI8" s="468"/>
-      <c r="AJ8" s="468"/>
-      <c r="AK8" s="468"/>
-      <c r="AL8" s="468"/>
-      <c r="AM8" s="468"/>
-      <c r="AN8" s="468"/>
-      <c r="AO8" s="470"/>
-      <c r="AP8" s="350" t="s">
+      <c r="Z8" s="457"/>
+      <c r="AA8" s="457"/>
+      <c r="AB8" s="457"/>
+      <c r="AC8" s="457"/>
+      <c r="AD8" s="457"/>
+      <c r="AE8" s="457"/>
+      <c r="AF8" s="457"/>
+      <c r="AG8" s="457"/>
+      <c r="AH8" s="457"/>
+      <c r="AI8" s="457"/>
+      <c r="AJ8" s="457"/>
+      <c r="AK8" s="457"/>
+      <c r="AL8" s="457"/>
+      <c r="AM8" s="457"/>
+      <c r="AN8" s="457"/>
+      <c r="AO8" s="459"/>
+      <c r="AP8" s="380" t="s">
         <v>16</v>
       </c>
-      <c r="AQ8" s="350" t="s">
+      <c r="AQ8" s="380" t="s">
         <v>17</v>
       </c>
-      <c r="AR8" s="350" t="s">
+      <c r="AR8" s="380" t="s">
         <v>18</v>
       </c>
-      <c r="AS8" s="350" t="s">
+      <c r="AS8" s="380" t="s">
         <v>19</v>
       </c>
-      <c r="AT8" s="350" t="s">
+      <c r="AT8" s="380" t="s">
         <v>20</v>
       </c>
-      <c r="AU8" s="350" t="s">
+      <c r="AU8" s="380" t="s">
         <v>21</v>
       </c>
-      <c r="AV8" s="444" t="s">
+      <c r="AV8" s="335" t="s">
         <v>22</v>
       </c>
-      <c r="AW8" s="359" t="s">
+      <c r="AW8" s="391" t="s">
         <v>23</v>
       </c>
-      <c r="AX8" s="444" t="s">
+      <c r="AX8" s="335" t="s">
         <v>24</v>
       </c>
-      <c r="AY8" s="469" t="s">
+      <c r="AY8" s="458" t="s">
         <v>25</v>
       </c>
-      <c r="AZ8" s="468"/>
-      <c r="BA8" s="468"/>
-      <c r="BB8" s="468"/>
-      <c r="BC8" s="468"/>
-      <c r="BD8" s="468"/>
-      <c r="BE8" s="468"/>
-      <c r="BF8" s="468"/>
-      <c r="BG8" s="468"/>
-      <c r="BH8" s="468"/>
-      <c r="BI8" s="468"/>
-      <c r="BJ8" s="468"/>
-      <c r="BK8" s="468"/>
-      <c r="BL8" s="468"/>
-      <c r="BM8" s="468"/>
-      <c r="BN8" s="468"/>
-      <c r="BO8" s="468"/>
-      <c r="BP8" s="470"/>
-      <c r="BQ8" s="459" t="s">
+      <c r="AZ8" s="457"/>
+      <c r="BA8" s="457"/>
+      <c r="BB8" s="457"/>
+      <c r="BC8" s="457"/>
+      <c r="BD8" s="457"/>
+      <c r="BE8" s="457"/>
+      <c r="BF8" s="457"/>
+      <c r="BG8" s="457"/>
+      <c r="BH8" s="457"/>
+      <c r="BI8" s="457"/>
+      <c r="BJ8" s="457"/>
+      <c r="BK8" s="457"/>
+      <c r="BL8" s="457"/>
+      <c r="BM8" s="457"/>
+      <c r="BN8" s="457"/>
+      <c r="BO8" s="457"/>
+      <c r="BP8" s="459"/>
+      <c r="BQ8" s="449" t="s">
         <v>26</v>
       </c>
-      <c r="BR8" s="417"/>
-      <c r="BS8" s="455" t="s">
+      <c r="BR8" s="415"/>
+      <c r="BS8" s="411" t="s">
         <v>143</v>
       </c>
-      <c r="BT8" s="455" t="s">
+      <c r="BT8" s="411" t="s">
         <v>27</v>
       </c>
-      <c r="BU8" s="456" t="s">
+      <c r="BU8" s="338" t="s">
         <v>29</v>
       </c>
-      <c r="BV8" s="446" t="s">
+      <c r="BV8" s="439" t="s">
         <v>30</v>
       </c>
-      <c r="BW8" s="447"/>
-      <c r="BX8" s="447"/>
-      <c r="BY8" s="448"/>
-      <c r="BZ8" s="356" t="s">
+      <c r="BW8" s="440"/>
+      <c r="BX8" s="440"/>
+      <c r="BY8" s="441"/>
+      <c r="BZ8" s="420" t="s">
         <v>31</v>
       </c>
-      <c r="CA8" s="356" t="s">
+      <c r="CA8" s="420" t="s">
         <v>32</v>
       </c>
-      <c r="CB8" s="388" t="s">
+      <c r="CB8" s="420" t="s">
         <v>33</v>
       </c>
-      <c r="CF8" s="241"/>
-      <c r="CG8" s="241"/>
+      <c r="CF8" s="331"/>
+      <c r="CG8" s="331"/>
     </row>
-    <row r="9" spans="1:85" s="284" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A9" s="439"/>
-      <c r="B9" s="439"/>
-      <c r="C9" s="439"/>
-      <c r="D9" s="439"/>
-      <c r="E9" s="439"/>
-      <c r="F9" s="439"/>
-      <c r="G9" s="351"/>
-      <c r="H9" s="439"/>
-      <c r="I9" s="439"/>
-      <c r="J9" s="351"/>
-      <c r="K9" s="438" t="s">
+    <row r="9" spans="1:85" s="330" customFormat="1" ht="19.25" customHeight="1">
+      <c r="A9" s="437"/>
+      <c r="B9" s="437"/>
+      <c r="C9" s="437"/>
+      <c r="D9" s="437"/>
+      <c r="E9" s="437"/>
+      <c r="F9" s="437"/>
+      <c r="G9" s="381"/>
+      <c r="H9" s="437"/>
+      <c r="I9" s="437"/>
+      <c r="J9" s="381"/>
+      <c r="K9" s="453" t="s">
         <v>34</v>
       </c>
-      <c r="L9" s="438" t="s">
+      <c r="L9" s="453" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="438" t="s">
+      <c r="M9" s="453" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="438" t="s">
+      <c r="N9" s="453" t="s">
         <v>37</v>
       </c>
-      <c r="O9" s="438" t="s">
+      <c r="O9" s="453" t="s">
         <v>38</v>
       </c>
-      <c r="P9" s="438" t="s">
+      <c r="P9" s="453" t="s">
         <v>39</v>
       </c>
-      <c r="Q9" s="438" t="s">
+      <c r="Q9" s="453" t="s">
         <v>40</v>
       </c>
-      <c r="R9" s="438" t="s">
+      <c r="R9" s="453" t="s">
         <v>41</v>
       </c>
-      <c r="S9" s="438" t="s">
+      <c r="S9" s="453" t="s">
         <v>42</v>
       </c>
-      <c r="T9" s="438" t="s">
+      <c r="T9" s="453" t="s">
         <v>43</v>
       </c>
-      <c r="U9" s="438" t="s">
+      <c r="U9" s="453" t="s">
         <v>44</v>
       </c>
-      <c r="V9" s="477" t="s">
+      <c r="V9" s="468" t="s">
         <v>45</v>
       </c>
-      <c r="W9" s="417"/>
-      <c r="X9" s="438" t="s">
+      <c r="W9" s="469"/>
+      <c r="X9" s="453" t="s">
         <v>46</v>
       </c>
-      <c r="Y9" s="442" t="s">
+      <c r="Y9" s="448" t="s">
         <v>47</v>
       </c>
-      <c r="Z9" s="442" t="s">
+      <c r="Z9" s="448" t="s">
         <v>48</v>
       </c>
-      <c r="AA9" s="442" t="s">
+      <c r="AA9" s="448" t="s">
         <v>49</v>
       </c>
-      <c r="AB9" s="442" t="s">
+      <c r="AB9" s="448" t="s">
         <v>50</v>
       </c>
-      <c r="AC9" s="442" t="s">
+      <c r="AC9" s="448" t="s">
         <v>51</v>
       </c>
-      <c r="AD9" s="442" t="s">
+      <c r="AD9" s="448" t="s">
         <v>144</v>
       </c>
-      <c r="AE9" s="442" t="s">
+      <c r="AE9" s="448" t="s">
         <v>53</v>
       </c>
-      <c r="AF9" s="442" t="s">
+      <c r="AF9" s="448" t="s">
         <v>54</v>
       </c>
-      <c r="AG9" s="442" t="s">
+      <c r="AG9" s="448" t="s">
         <v>55</v>
       </c>
-      <c r="AH9" s="442" t="s">
+      <c r="AH9" s="448" t="s">
         <v>56</v>
       </c>
-      <c r="AI9" s="442" t="s">
+      <c r="AI9" s="448" t="s">
         <v>57</v>
       </c>
-      <c r="AJ9" s="464" t="s">
+      <c r="AJ9" s="386" t="s">
         <v>58</v>
       </c>
-      <c r="AK9" s="478" t="s">
+      <c r="AK9" s="388" t="s">
         <v>59</v>
       </c>
-      <c r="AL9" s="359" t="s">
+      <c r="AL9" s="391" t="s">
         <v>60</v>
       </c>
-      <c r="AM9" s="481" t="s">
+      <c r="AM9" s="341" t="s">
         <v>61</v>
       </c>
-      <c r="AN9" s="444" t="s">
+      <c r="AN9" s="335" t="s">
         <v>62</v>
       </c>
-      <c r="AO9" s="444" t="s">
+      <c r="AO9" s="335" t="s">
         <v>63</v>
       </c>
-      <c r="AP9" s="351"/>
-      <c r="AQ9" s="351"/>
-      <c r="AR9" s="351"/>
-      <c r="AS9" s="351"/>
-      <c r="AT9" s="351"/>
-      <c r="AU9" s="351"/>
-      <c r="AV9" s="347"/>
-      <c r="AW9" s="351"/>
-      <c r="AX9" s="347"/>
-      <c r="AY9" s="443" t="s">
+      <c r="AP9" s="381"/>
+      <c r="AQ9" s="381"/>
+      <c r="AR9" s="381"/>
+      <c r="AS9" s="381"/>
+      <c r="AT9" s="381"/>
+      <c r="AU9" s="381"/>
+      <c r="AV9" s="336"/>
+      <c r="AW9" s="381"/>
+      <c r="AX9" s="336"/>
+      <c r="AY9" s="467" t="s">
         <v>25</v>
       </c>
-      <c r="AZ9" s="404"/>
-      <c r="BA9" s="404"/>
-      <c r="BB9" s="404"/>
-      <c r="BC9" s="404"/>
-      <c r="BD9" s="404"/>
-      <c r="BE9" s="404"/>
-      <c r="BF9" s="404"/>
-      <c r="BG9" s="404"/>
-      <c r="BH9" s="404"/>
-      <c r="BI9" s="404"/>
-      <c r="BJ9" s="405"/>
-      <c r="BK9" s="443" t="s">
+      <c r="AZ9" s="402"/>
+      <c r="BA9" s="402"/>
+      <c r="BB9" s="402"/>
+      <c r="BC9" s="402"/>
+      <c r="BD9" s="402"/>
+      <c r="BE9" s="402"/>
+      <c r="BF9" s="402"/>
+      <c r="BG9" s="402"/>
+      <c r="BH9" s="402"/>
+      <c r="BI9" s="402"/>
+      <c r="BJ9" s="403"/>
+      <c r="BK9" s="467" t="s">
         <v>64</v>
       </c>
-      <c r="BL9" s="404"/>
-      <c r="BM9" s="404"/>
-      <c r="BN9" s="404"/>
-      <c r="BO9" s="404"/>
-      <c r="BP9" s="405"/>
-      <c r="BQ9" s="476" t="s">
+      <c r="BL9" s="402"/>
+      <c r="BM9" s="402"/>
+      <c r="BN9" s="402"/>
+      <c r="BO9" s="402"/>
+      <c r="BP9" s="403"/>
+      <c r="BQ9" s="466" t="s">
         <v>65</v>
       </c>
-      <c r="BR9" s="476" t="s">
+      <c r="BR9" s="466" t="s">
         <v>66</v>
       </c>
-      <c r="BS9" s="439"/>
-      <c r="BT9" s="439"/>
-      <c r="BU9" s="457"/>
-      <c r="BV9" s="449"/>
-      <c r="BW9" s="450"/>
-      <c r="BX9" s="450"/>
-      <c r="BY9" s="451"/>
-      <c r="BZ9" s="439"/>
-      <c r="CA9" s="439"/>
-      <c r="CB9" s="351"/>
-      <c r="CF9" s="241"/>
-      <c r="CG9" s="241"/>
+      <c r="BS9" s="437"/>
+      <c r="BT9" s="437"/>
+      <c r="BU9" s="339"/>
+      <c r="BV9" s="442"/>
+      <c r="BW9" s="443"/>
+      <c r="BX9" s="443"/>
+      <c r="BY9" s="444"/>
+      <c r="BZ9" s="437"/>
+      <c r="CA9" s="437"/>
+      <c r="CB9" s="437"/>
+      <c r="CF9" s="331"/>
+      <c r="CG9" s="331"/>
     </row>
-    <row r="10" spans="1:85" s="279" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A10" s="439"/>
-      <c r="B10" s="439"/>
-      <c r="C10" s="439"/>
-      <c r="D10" s="439"/>
-      <c r="E10" s="439"/>
-      <c r="F10" s="439"/>
-      <c r="G10" s="351"/>
-      <c r="H10" s="439"/>
-      <c r="I10" s="439"/>
-      <c r="J10" s="351"/>
-      <c r="K10" s="439"/>
-      <c r="L10" s="439"/>
-      <c r="M10" s="439"/>
-      <c r="N10" s="439"/>
-      <c r="O10" s="439"/>
-      <c r="P10" s="439"/>
-      <c r="Q10" s="439"/>
-      <c r="R10" s="439"/>
-      <c r="S10" s="439"/>
-      <c r="T10" s="439"/>
-      <c r="U10" s="439"/>
-      <c r="V10" s="411"/>
-      <c r="W10" s="418"/>
-      <c r="X10" s="439"/>
-      <c r="Y10" s="439"/>
-      <c r="Z10" s="439"/>
-      <c r="AA10" s="439"/>
-      <c r="AB10" s="439"/>
-      <c r="AC10" s="439"/>
-      <c r="AD10" s="439"/>
-      <c r="AE10" s="439"/>
-      <c r="AF10" s="439"/>
-      <c r="AG10" s="439"/>
-      <c r="AH10" s="439"/>
-      <c r="AI10" s="439"/>
-      <c r="AJ10" s="351"/>
-      <c r="AK10" s="479"/>
-      <c r="AL10" s="351"/>
-      <c r="AM10" s="347"/>
-      <c r="AN10" s="347"/>
-      <c r="AO10" s="347"/>
-      <c r="AP10" s="351"/>
-      <c r="AQ10" s="351"/>
-      <c r="AR10" s="351"/>
-      <c r="AS10" s="351"/>
-      <c r="AT10" s="351"/>
-      <c r="AU10" s="351"/>
-      <c r="AV10" s="347"/>
-      <c r="AW10" s="351"/>
-      <c r="AX10" s="347"/>
-      <c r="AY10" s="320" t="s">
+    <row r="10" spans="1:85" s="332" customFormat="1" ht="19.25" customHeight="1">
+      <c r="A10" s="437"/>
+      <c r="B10" s="437"/>
+      <c r="C10" s="437"/>
+      <c r="D10" s="437"/>
+      <c r="E10" s="437"/>
+      <c r="F10" s="437"/>
+      <c r="G10" s="381"/>
+      <c r="H10" s="437"/>
+      <c r="I10" s="437"/>
+      <c r="J10" s="381"/>
+      <c r="K10" s="437"/>
+      <c r="L10" s="437"/>
+      <c r="M10" s="437"/>
+      <c r="N10" s="437"/>
+      <c r="O10" s="437"/>
+      <c r="P10" s="437"/>
+      <c r="Q10" s="437"/>
+      <c r="R10" s="437"/>
+      <c r="S10" s="437"/>
+      <c r="T10" s="437"/>
+      <c r="U10" s="437"/>
+      <c r="V10" s="470"/>
+      <c r="W10" s="471"/>
+      <c r="X10" s="437"/>
+      <c r="Y10" s="437"/>
+      <c r="Z10" s="437"/>
+      <c r="AA10" s="437"/>
+      <c r="AB10" s="437"/>
+      <c r="AC10" s="437"/>
+      <c r="AD10" s="437"/>
+      <c r="AE10" s="437"/>
+      <c r="AF10" s="437"/>
+      <c r="AG10" s="437"/>
+      <c r="AH10" s="437"/>
+      <c r="AI10" s="437"/>
+      <c r="AJ10" s="381"/>
+      <c r="AK10" s="389"/>
+      <c r="AL10" s="381"/>
+      <c r="AM10" s="336"/>
+      <c r="AN10" s="336"/>
+      <c r="AO10" s="336"/>
+      <c r="AP10" s="381"/>
+      <c r="AQ10" s="381"/>
+      <c r="AR10" s="381"/>
+      <c r="AS10" s="381"/>
+      <c r="AT10" s="381"/>
+      <c r="AU10" s="381"/>
+      <c r="AV10" s="336"/>
+      <c r="AW10" s="381"/>
+      <c r="AX10" s="336"/>
+      <c r="AY10" s="329" t="s">
         <v>67</v>
       </c>
-      <c r="AZ10" s="320" t="s">
+      <c r="AZ10" s="329" t="s">
         <v>68</v>
       </c>
-      <c r="BA10" s="320" t="s">
+      <c r="BA10" s="329" t="s">
         <v>69</v>
       </c>
-      <c r="BB10" s="475" t="s">
+      <c r="BB10" s="465" t="s">
         <v>70</v>
       </c>
-      <c r="BC10" s="466" t="s">
+      <c r="BC10" s="455" t="s">
         <v>71</v>
       </c>
-      <c r="BD10" s="466" t="s">
+      <c r="BD10" s="455" t="s">
         <v>72</v>
       </c>
-      <c r="BE10" s="441" t="s">
+      <c r="BE10" s="451" t="s">
         <v>145</v>
       </c>
-      <c r="BF10" s="441" t="s">
+      <c r="BF10" s="451" t="s">
         <v>74</v>
       </c>
-      <c r="BG10" s="441" t="s">
+      <c r="BG10" s="451" t="s">
         <v>75</v>
       </c>
-      <c r="BH10" s="466" t="s">
+      <c r="BH10" s="455" t="s">
         <v>76</v>
       </c>
-      <c r="BI10" s="441" t="s">
+      <c r="BI10" s="451" t="s">
         <v>79</v>
       </c>
-      <c r="BJ10" s="483" t="s">
+      <c r="BJ10" s="474" t="s">
         <v>80</v>
       </c>
-      <c r="BK10" s="466" t="s">
+      <c r="BK10" s="455" t="s">
         <v>81</v>
       </c>
-      <c r="BL10" s="461" t="s">
+      <c r="BL10" s="452" t="s">
         <v>82</v>
       </c>
-      <c r="BM10" s="466" t="s">
+      <c r="BM10" s="455" t="s">
         <v>83</v>
       </c>
-      <c r="BN10" s="461" t="s">
+      <c r="BN10" s="452" t="s">
         <v>84</v>
       </c>
-      <c r="BO10" s="461" t="s">
+      <c r="BO10" s="452" t="s">
         <v>146</v>
       </c>
-      <c r="BP10" s="455" t="s">
+      <c r="BP10" s="411" t="s">
         <v>85</v>
       </c>
-      <c r="BQ10" s="439"/>
-      <c r="BR10" s="439"/>
-      <c r="BS10" s="439"/>
-      <c r="BT10" s="439"/>
-      <c r="BU10" s="457"/>
-      <c r="BV10" s="452"/>
-      <c r="BW10" s="453"/>
-      <c r="BX10" s="453"/>
-      <c r="BY10" s="454"/>
-      <c r="BZ10" s="439"/>
-      <c r="CA10" s="439"/>
-      <c r="CB10" s="351"/>
+      <c r="BQ10" s="437"/>
+      <c r="BR10" s="437"/>
+      <c r="BS10" s="437"/>
+      <c r="BT10" s="437"/>
+      <c r="BU10" s="339"/>
+      <c r="BV10" s="445"/>
+      <c r="BW10" s="446"/>
+      <c r="BX10" s="446"/>
+      <c r="BY10" s="447"/>
+      <c r="BZ10" s="437"/>
+      <c r="CA10" s="437"/>
+      <c r="CB10" s="437"/>
       <c r="CC10" s="228" t="s">
         <v>3</v>
       </c>
-      <c r="CF10" s="241"/>
-      <c r="CG10" s="241"/>
+      <c r="CF10" s="331"/>
+      <c r="CG10" s="331"/>
     </row>
-    <row r="11" spans="1:85" s="279" customFormat="1" ht="38.25" customHeight="1">
-      <c r="A11" s="440"/>
-      <c r="B11" s="440"/>
-      <c r="C11" s="440"/>
-      <c r="D11" s="440"/>
-      <c r="E11" s="440"/>
-      <c r="F11" s="440"/>
-      <c r="G11" s="345"/>
-      <c r="H11" s="440"/>
-      <c r="I11" s="440"/>
-      <c r="J11" s="345"/>
-      <c r="K11" s="440"/>
-      <c r="L11" s="440"/>
-      <c r="M11" s="440"/>
-      <c r="N11" s="440"/>
-      <c r="O11" s="440"/>
-      <c r="P11" s="440"/>
-      <c r="Q11" s="440"/>
-      <c r="R11" s="440"/>
-      <c r="S11" s="440"/>
-      <c r="T11" s="440"/>
-      <c r="U11" s="440"/>
-      <c r="V11" s="321" t="s">
+    <row r="11" spans="1:85" s="332" customFormat="1" ht="38.25" customHeight="1">
+      <c r="A11" s="438"/>
+      <c r="B11" s="438"/>
+      <c r="C11" s="438"/>
+      <c r="D11" s="438"/>
+      <c r="E11" s="438"/>
+      <c r="F11" s="438"/>
+      <c r="G11" s="382"/>
+      <c r="H11" s="438"/>
+      <c r="I11" s="438"/>
+      <c r="J11" s="382"/>
+      <c r="K11" s="438"/>
+      <c r="L11" s="438"/>
+      <c r="M11" s="438"/>
+      <c r="N11" s="438"/>
+      <c r="O11" s="438"/>
+      <c r="P11" s="438"/>
+      <c r="Q11" s="438"/>
+      <c r="R11" s="438"/>
+      <c r="S11" s="438"/>
+      <c r="T11" s="438"/>
+      <c r="U11" s="438"/>
+      <c r="V11" s="333" t="s">
         <v>86</v>
       </c>
-      <c r="W11" s="321" t="s">
+      <c r="W11" s="333" t="s">
         <v>87</v>
       </c>
-      <c r="X11" s="440"/>
-      <c r="Y11" s="440"/>
-      <c r="Z11" s="440"/>
-      <c r="AA11" s="440"/>
-      <c r="AB11" s="440"/>
-      <c r="AC11" s="440"/>
-      <c r="AD11" s="440"/>
-      <c r="AE11" s="440"/>
-      <c r="AF11" s="440"/>
-      <c r="AG11" s="440"/>
-      <c r="AH11" s="440"/>
-      <c r="AI11" s="440"/>
-      <c r="AJ11" s="345"/>
-      <c r="AK11" s="480"/>
-      <c r="AL11" s="345"/>
-      <c r="AM11" s="348"/>
-      <c r="AN11" s="348"/>
-      <c r="AO11" s="348"/>
-      <c r="AP11" s="345"/>
-      <c r="AQ11" s="345"/>
-      <c r="AR11" s="345"/>
-      <c r="AS11" s="345"/>
-      <c r="AT11" s="345"/>
-      <c r="AU11" s="345"/>
-      <c r="AV11" s="348"/>
-      <c r="AW11" s="345"/>
-      <c r="AX11" s="348"/>
+      <c r="X11" s="438"/>
+      <c r="Y11" s="438"/>
+      <c r="Z11" s="438"/>
+      <c r="AA11" s="438"/>
+      <c r="AB11" s="438"/>
+      <c r="AC11" s="438"/>
+      <c r="AD11" s="438"/>
+      <c r="AE11" s="438"/>
+      <c r="AF11" s="438"/>
+      <c r="AG11" s="438"/>
+      <c r="AH11" s="438"/>
+      <c r="AI11" s="438"/>
+      <c r="AJ11" s="382"/>
+      <c r="AK11" s="390"/>
+      <c r="AL11" s="382"/>
+      <c r="AM11" s="337"/>
+      <c r="AN11" s="337"/>
+      <c r="AO11" s="337"/>
+      <c r="AP11" s="382"/>
+      <c r="AQ11" s="382"/>
+      <c r="AR11" s="382"/>
+      <c r="AS11" s="382"/>
+      <c r="AT11" s="382"/>
+      <c r="AU11" s="382"/>
+      <c r="AV11" s="337"/>
+      <c r="AW11" s="382"/>
+      <c r="AX11" s="337"/>
       <c r="AY11" s="229" t="s">
         <v>88</v>
       </c>
@@ -15929,50 +15934,50 @@
       <c r="BA11" s="229" t="s">
         <v>90</v>
       </c>
-      <c r="BB11" s="440"/>
-      <c r="BC11" s="345"/>
-      <c r="BD11" s="345"/>
-      <c r="BE11" s="440"/>
-      <c r="BF11" s="440"/>
-      <c r="BG11" s="440"/>
-      <c r="BH11" s="345"/>
-      <c r="BI11" s="440"/>
-      <c r="BJ11" s="440"/>
-      <c r="BK11" s="345"/>
-      <c r="BL11" s="345"/>
-      <c r="BM11" s="345"/>
-      <c r="BN11" s="345"/>
-      <c r="BO11" s="345"/>
-      <c r="BP11" s="440"/>
-      <c r="BQ11" s="440"/>
-      <c r="BR11" s="440"/>
-      <c r="BS11" s="440"/>
-      <c r="BT11" s="440"/>
-      <c r="BU11" s="458"/>
-      <c r="BV11" s="332" t="s">
+      <c r="BB11" s="438"/>
+      <c r="BC11" s="382"/>
+      <c r="BD11" s="382"/>
+      <c r="BE11" s="438"/>
+      <c r="BF11" s="438"/>
+      <c r="BG11" s="438"/>
+      <c r="BH11" s="382"/>
+      <c r="BI11" s="438"/>
+      <c r="BJ11" s="438"/>
+      <c r="BK11" s="382"/>
+      <c r="BL11" s="382"/>
+      <c r="BM11" s="382"/>
+      <c r="BN11" s="382"/>
+      <c r="BO11" s="382"/>
+      <c r="BP11" s="438"/>
+      <c r="BQ11" s="438"/>
+      <c r="BR11" s="438"/>
+      <c r="BS11" s="438"/>
+      <c r="BT11" s="438"/>
+      <c r="BU11" s="340"/>
+      <c r="BV11" s="237" t="s">
         <v>91</v>
       </c>
-      <c r="BW11" s="332" t="s">
+      <c r="BW11" s="237" t="s">
         <v>92</v>
       </c>
-      <c r="BX11" s="332" t="s">
+      <c r="BX11" s="237" t="s">
         <v>93</v>
       </c>
-      <c r="BY11" s="333" t="s">
+      <c r="BY11" s="238" t="s">
         <v>94</v>
       </c>
-      <c r="BZ11" s="463"/>
-      <c r="CA11" s="463"/>
-      <c r="CB11" s="389"/>
+      <c r="BZ11" s="462"/>
+      <c r="CA11" s="462"/>
+      <c r="CB11" s="462"/>
       <c r="CC11" s="227">
         <v>25</v>
       </c>
-      <c r="CD11" s="285"/>
-      <c r="CF11" s="241"/>
-      <c r="CG11" s="241"/>
+      <c r="CD11" s="334"/>
+      <c r="CF11" s="331"/>
+      <c r="CG11" s="331"/>
     </row>
     <row r="12" spans="1:85" s="278" customFormat="1" ht="15" customHeight="1">
-      <c r="A12" s="286">
+      <c r="A12" s="284">
         <v>1</v>
       </c>
       <c r="B12" s="276">
@@ -16268,25 +16273,25 @@
       <c r="CG12" s="241"/>
     </row>
     <row r="13" spans="1:85" s="278" customFormat="1" ht="15" customHeight="1">
-      <c r="A13" s="286" t="s">
+      <c r="A13" s="284" t="s">
         <v>96</v>
       </c>
-      <c r="B13" s="286" t="s">
+      <c r="B13" s="284" t="s">
         <v>96</v>
       </c>
-      <c r="C13" s="286" t="s">
+      <c r="C13" s="284" t="s">
         <v>96</v>
       </c>
       <c r="D13" s="276"/>
       <c r="E13" s="276"/>
       <c r="F13" s="276"/>
-      <c r="G13" s="286" t="s">
+      <c r="G13" s="284" t="s">
         <v>96</v>
       </c>
-      <c r="H13" s="286" t="s">
+      <c r="H13" s="284" t="s">
         <v>96</v>
       </c>
-      <c r="I13" s="286" t="s">
+      <c r="I13" s="284" t="s">
         <v>96</v>
       </c>
       <c r="J13" s="276"/>
@@ -16384,38 +16389,38 @@
         <v>185460000</v>
       </c>
       <c r="J14" s="249"/>
-      <c r="K14" s="287">
+      <c r="K14" s="285">
         <f>SUM(K15:K21)</f>
         <v>75.5</v>
       </c>
-      <c r="L14" s="287"/>
-      <c r="M14" s="287"/>
-      <c r="N14" s="287"/>
-      <c r="O14" s="287"/>
-      <c r="P14" s="287"/>
-      <c r="Q14" s="287"/>
-      <c r="R14" s="287">
+      <c r="L14" s="285"/>
+      <c r="M14" s="285"/>
+      <c r="N14" s="285"/>
+      <c r="O14" s="285"/>
+      <c r="P14" s="285"/>
+      <c r="Q14" s="285"/>
+      <c r="R14" s="285">
         <f>SUM(R15:R21)</f>
         <v>12</v>
       </c>
-      <c r="S14" s="287">
+      <c r="S14" s="285">
         <f>SUM(S15:S21)</f>
         <v>0</v>
       </c>
-      <c r="T14" s="287"/>
-      <c r="U14" s="287">
+      <c r="T14" s="285"/>
+      <c r="U14" s="285">
         <f>SUM(U15:U21)</f>
         <v>0</v>
       </c>
-      <c r="V14" s="287">
+      <c r="V14" s="285">
         <f>SUM(V15:V21)</f>
         <v>0</v>
       </c>
-      <c r="W14" s="287">
+      <c r="W14" s="285">
         <f>SUM(W15:W21)</f>
         <v>0</v>
       </c>
-      <c r="X14" s="287">
+      <c r="X14" s="285">
         <f>SUM(X15:X21)</f>
         <v>0</v>
       </c>
@@ -16558,207 +16563,207 @@
       <c r="CB14" s="243"/>
     </row>
     <row r="15" spans="1:85" s="253" customFormat="1" ht="30.5" customHeight="1">
-      <c r="A15" s="322">
+      <c r="A15" s="318">
         <f>IF(B15=0,"",COUNTA($B$15:(B15)))</f>
         <v>1</v>
       </c>
-      <c r="B15" s="323">
+      <c r="B15" s="319">
         <v>2405236</v>
       </c>
-      <c r="C15" s="324" t="s">
+      <c r="C15" s="320" t="s">
         <v>97</v>
       </c>
-      <c r="D15" s="325" t="s">
+      <c r="D15" s="321" t="s">
         <v>98</v>
       </c>
-      <c r="E15" s="326" t="s">
+      <c r="E15" s="322" t="s">
         <v>113</v>
       </c>
-      <c r="F15" s="326" t="s">
+      <c r="F15" s="322" t="s">
         <v>100</v>
       </c>
-      <c r="G15" s="327">
+      <c r="G15" s="323">
         <v>9520000</v>
       </c>
-      <c r="H15" s="327">
+      <c r="H15" s="323">
         <f t="shared" ref="H15:H21" si="4">+IF(OR(CA15="ĐT PCCC",CA15="ĐP PCCC"),780000,IF(CA15="AT-VSV",300000,0))</f>
         <v>0</v>
       </c>
-      <c r="I15" s="327">
+      <c r="I15" s="323">
         <f t="shared" ref="I15:I21" si="5">BZ15-BX15-G15-H15</f>
         <v>53480000</v>
       </c>
-      <c r="J15" s="328">
+      <c r="J15" s="324">
         <v>1</v>
       </c>
-      <c r="K15" s="329">
+      <c r="K15" s="325">
         <v>11</v>
       </c>
-      <c r="L15" s="329"/>
-      <c r="M15" s="329"/>
-      <c r="N15" s="329"/>
-      <c r="O15" s="329">
+      <c r="L15" s="325"/>
+      <c r="M15" s="325"/>
+      <c r="N15" s="325"/>
+      <c r="O15" s="325">
         <v>2</v>
       </c>
-      <c r="P15" s="329"/>
-      <c r="Q15" s="329"/>
-      <c r="R15" s="329">
-        <v>0</v>
-      </c>
-      <c r="S15" s="329">
-        <v>0</v>
-      </c>
-      <c r="T15" s="329"/>
-      <c r="U15" s="329">
-        <v>0</v>
-      </c>
-      <c r="V15" s="329">
-        <v>0</v>
-      </c>
-      <c r="W15" s="329">
-        <v>0</v>
-      </c>
-      <c r="X15" s="329">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="327">
+      <c r="P15" s="325"/>
+      <c r="Q15" s="325"/>
+      <c r="R15" s="325">
+        <v>0</v>
+      </c>
+      <c r="S15" s="325">
+        <v>0</v>
+      </c>
+      <c r="T15" s="325"/>
+      <c r="U15" s="325">
+        <v>0</v>
+      </c>
+      <c r="V15" s="325">
+        <v>0</v>
+      </c>
+      <c r="W15" s="325">
+        <v>0</v>
+      </c>
+      <c r="X15" s="325">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="323">
         <f t="shared" ref="Y15:Y21" si="6">G15*(K15+L15)/26</f>
         <v>4027692.3076923075</v>
       </c>
-      <c r="Z15" s="327">
+      <c r="Z15" s="323">
         <f t="shared" ref="Z15:Z21" si="7">M15*G15/26</f>
         <v>0</v>
       </c>
-      <c r="AA15" s="327">
+      <c r="AA15" s="323">
         <f t="shared" ref="AA15:AA21" si="8">G15*N15/26</f>
         <v>0</v>
       </c>
-      <c r="AB15" s="327">
+      <c r="AB15" s="323">
         <f t="shared" ref="AB15:AB21" si="9">G15*O15/26</f>
         <v>732307.69230769225</v>
       </c>
-      <c r="AC15" s="327">
+      <c r="AC15" s="323">
         <f t="shared" ref="AC15:AC21" si="10">G15*P15*150%/26</f>
         <v>0</v>
       </c>
-      <c r="AD15" s="327">
+      <c r="AD15" s="323">
         <f t="shared" ref="AD15:AD21" si="11">G15*Q15/26*200%</f>
         <v>0</v>
       </c>
-      <c r="AE15" s="327">
+      <c r="AE15" s="323">
         <f t="shared" ref="AE15:AE21" si="12">G15*R15/26*300%</f>
         <v>0</v>
       </c>
-      <c r="AF15" s="327">
+      <c r="AF15" s="323">
         <f t="shared" ref="AF15:AF21" si="13">IF(F15="LT",0,(G15+H15)/26*S15*30%)</f>
         <v>0</v>
       </c>
-      <c r="AG15" s="327">
+      <c r="AG15" s="323">
         <f t="shared" ref="AG15:AG21" si="14">T15*G15/23/8</f>
         <v>0</v>
       </c>
-      <c r="AH15" s="327">
+      <c r="AH15" s="323">
         <f t="shared" ref="AH15:AH21" si="15">BZ15/26*U15</f>
         <v>0</v>
       </c>
-      <c r="AI15" s="327">
+      <c r="AI15" s="323">
         <f t="shared" ref="AI15:AI21" si="16">G15*V15/26</f>
         <v>0</v>
       </c>
-      <c r="AJ15" s="327"/>
-      <c r="AK15" s="327">
+      <c r="AJ15" s="323"/>
+      <c r="AK15" s="323">
         <f t="shared" ref="AK15:AK21" si="17">BX15*L15/26</f>
         <v>0</v>
       </c>
-      <c r="AL15" s="327"/>
-      <c r="AM15" s="327">
+      <c r="AL15" s="323"/>
+      <c r="AM15" s="323">
         <f t="shared" ref="AM15:AM21" si="18">X15*CB15</f>
         <v>0</v>
       </c>
-      <c r="AN15" s="327">
+      <c r="AN15" s="323">
         <f>H15/26*(K15+L15)</f>
         <v>0</v>
       </c>
-      <c r="AO15" s="327">
+      <c r="AO15" s="323">
         <f t="shared" ref="AO15:AO21" si="19">IF(F15="LN",I15*(K15+L15)/26+(H15+I15)*50%*M15/26+IF(F15="LT",BU15*O15/26-AB15,0)+MAX($G15*P15/26*150%,P15*$BU15/26)-AC15+MAX($G15*Q15/26*200%,Q15*$BU15/26)-AD15+MAX($G15*R15/26*300%,R15*$BU15/26)-AE15+BU15*S15/26-AF15+AH15-AG15,I15-I15*($CC$11-K15-L15)/26+(H15+I15)*50%*M15/26+IF(F15="LT",BU15*O15/26-AB15,0)+MAX($G15*P15/26*150%,P15*$BU15/26)-AC15+MAX($G15*Q15/26*200%,Q15*$BU15/26)-AD15+MAX($G15*R15/26*300%,R15*$BU15/26)-AE15+BU15*S15/26-AF15+AH15-AG15+(G15-G15*($CC$11-K15-L15)/26-Y15)+(H15-H15*($CC$11-K15-L15)/26-AN15))</f>
         <v>28932307.692307696</v>
       </c>
-      <c r="AP15" s="327"/>
-      <c r="AQ15" s="327"/>
+      <c r="AP15" s="323"/>
+      <c r="AQ15" s="323"/>
       <c r="AR15" s="184">
         <v>1000000</v>
       </c>
-      <c r="AS15" s="327"/>
-      <c r="AT15" s="327"/>
-      <c r="AU15" s="327"/>
-      <c r="AV15" s="327">
+      <c r="AS15" s="323"/>
+      <c r="AT15" s="323"/>
+      <c r="AU15" s="323"/>
+      <c r="AV15" s="323">
         <f t="shared" ref="AV15:AV21" si="20">Y15+Z15+AA15+AB15+AC15+AD15+AE15+AF15+AG15+AI15+AJ15+AK15+AL15+AM15+AN15+AO15+AP15-AQ15+AR15+AS15+AT15+AU15</f>
         <v>34692307.692307696</v>
       </c>
-      <c r="AW15" s="327"/>
-      <c r="AX15" s="327" t="s">
+      <c r="AW15" s="323"/>
+      <c r="AX15" s="323" t="s">
         <v>101</v>
       </c>
-      <c r="AY15" s="330">
+      <c r="AY15" s="326">
         <f t="shared" ref="AY15:BA21" si="21">ROUND(IF($AX15="x",($G15+$H15)*AY$11,0),0)</f>
         <v>761600</v>
       </c>
-      <c r="AZ15" s="330">
+      <c r="AZ15" s="326">
         <f t="shared" si="21"/>
         <v>142800</v>
       </c>
-      <c r="BA15" s="330">
+      <c r="BA15" s="326">
         <f t="shared" si="21"/>
         <v>95200</v>
       </c>
-      <c r="BB15" s="330">
+      <c r="BB15" s="326">
         <f t="shared" ref="BB15:BB21" si="22">SUM(AY15:BA15)</f>
         <v>999600</v>
       </c>
-      <c r="BC15" s="330"/>
-      <c r="BD15" s="330"/>
-      <c r="BE15" s="330">
+      <c r="BC15" s="326"/>
+      <c r="BD15" s="326"/>
+      <c r="BE15" s="326">
         <f t="shared" ref="BE15:BE21" si="23">IF(G15*1%&gt;=234000,234000,G15*1%)</f>
         <v>95200</v>
       </c>
-      <c r="BF15" s="330">
+      <c r="BF15" s="326">
         <f>AM15+IF(AR15&gt;=730000,730000,AR15)+IF(((AV15-AM15-IF(AR15&gt;=730000,730000,AR15)-AS15)*15%-AS15)&gt;0,((AV15-AM15-IF(AR15&gt;=730000,730000,AR15)-AS15)*15%-AS15),0)</f>
         <v>5824346.153846154</v>
       </c>
-      <c r="BG15" s="330">
+      <c r="BG15" s="326">
         <f t="shared" ref="BG15:BG21" si="24">AV15-BF15+AW15</f>
         <v>28867961.538461544</v>
       </c>
-      <c r="BH15" s="330">
+      <c r="BH15" s="326">
         <v>3</v>
       </c>
-      <c r="BI15" s="330">
+      <c r="BI15" s="326">
         <f t="shared" ref="BI15:BI21" si="25">BG15-BB15-BC15+BD15-BH15*4400000-IF(E15="CT",11000000,0)</f>
         <v>14668361.538461544</v>
       </c>
-      <c r="BJ15" s="331">
+      <c r="BJ15" s="327">
         <f t="shared" ref="BJ15:BJ21" si="26">IF(BI15&gt;0,ROUND(IF(BI15&gt;=80000000,BI15*35%-9850000,IF(BI15&gt;=52000000,BI15*30%-5850000,IF(BI15&gt;=32000000,BI15*25%-3250000,IF(BI15&gt;=18000000,BI15*20%-1650000,IF(BI15&gt;=10000000,BI15*15%-750000,IF(BI15&gt;5000000,BI15*10%-250000,BI15*5%)))))),0),0)</f>
         <v>1450254</v>
       </c>
-      <c r="BK15" s="330"/>
-      <c r="BL15" s="330"/>
-      <c r="BM15" s="330">
-        <v>0</v>
-      </c>
-      <c r="BN15" s="330"/>
-      <c r="BO15" s="330"/>
-      <c r="BP15" s="330"/>
-      <c r="BQ15" s="330"/>
-      <c r="BR15" s="330"/>
-      <c r="BS15" s="330" t="str">
+      <c r="BK15" s="326"/>
+      <c r="BL15" s="326"/>
+      <c r="BM15" s="326">
+        <v>0</v>
+      </c>
+      <c r="BN15" s="326"/>
+      <c r="BO15" s="326"/>
+      <c r="BP15" s="326"/>
+      <c r="BQ15" s="326"/>
+      <c r="BR15" s="326"/>
+      <c r="BS15" s="326" t="str">
         <f t="shared" ref="BS15:BS21" si="27">IF(AV15&gt;=11000000,"80%","100%")</f>
         <v>80%</v>
       </c>
-      <c r="BT15" s="330">
+      <c r="BT15" s="326">
         <f>AV15*BS15-BN15-BK15-BP15-BO15</f>
         <v>27753846.15384616</v>
       </c>
-      <c r="BU15" s="334">
+      <c r="BU15" s="328">
         <v>60000000</v>
       </c>
       <c r="BV15" s="188">
@@ -16768,21 +16773,21 @@
       <c r="BX15" s="188">
         <v>200000</v>
       </c>
-      <c r="BY15" s="331">
+      <c r="BY15" s="327">
         <f t="shared" ref="BY15:BY21" si="28">+BU15*5%</f>
         <v>3000000</v>
       </c>
-      <c r="BZ15" s="331">
+      <c r="BZ15" s="327">
         <f t="shared" ref="BZ15:BZ21" si="29">SUM(BU15:BY15)</f>
         <v>63200000</v>
       </c>
-      <c r="CA15" s="331" t="s">
+      <c r="CA15" s="327" t="s">
         <v>122</v>
       </c>
-      <c r="CB15" s="331"/>
-      <c r="CC15" s="289"/>
-      <c r="CD15" s="290"/>
-      <c r="CE15" s="290"/>
+      <c r="CB15" s="327"/>
+      <c r="CC15" s="287"/>
+      <c r="CD15" s="288"/>
+      <c r="CE15" s="288"/>
       <c r="CF15" s="252"/>
       <c r="CG15" s="252"/>
     </row>
@@ -16817,7 +16822,7 @@
         <f t="shared" si="5"/>
         <v>43520000</v>
       </c>
-      <c r="J16" s="288">
+      <c r="J16" s="286">
         <v>1</v>
       </c>
       <c r="K16" s="250">
@@ -17011,9 +17016,9 @@
         <v>114</v>
       </c>
       <c r="CB16" s="243"/>
-      <c r="CC16" s="289"/>
-      <c r="CD16" s="290"/>
-      <c r="CE16" s="290"/>
+      <c r="CC16" s="287"/>
+      <c r="CD16" s="288"/>
+      <c r="CE16" s="288"/>
       <c r="CF16" s="252"/>
       <c r="CG16" s="252"/>
     </row>
@@ -17048,7 +17053,7 @@
         <f t="shared" si="5"/>
         <v>33880000</v>
       </c>
-      <c r="J17" s="288">
+      <c r="J17" s="286">
         <v>1</v>
       </c>
       <c r="K17" s="250">
@@ -17240,9 +17245,9 @@
         <v>118</v>
       </c>
       <c r="CB17" s="243"/>
-      <c r="CC17" s="289"/>
-      <c r="CD17" s="290"/>
-      <c r="CE17" s="290"/>
+      <c r="CC17" s="287"/>
+      <c r="CD17" s="288"/>
+      <c r="CE17" s="288"/>
       <c r="CF17" s="252"/>
       <c r="CG17" s="252"/>
     </row>
@@ -17277,7 +17282,7 @@
         <f t="shared" si="5"/>
         <v>19160000</v>
       </c>
-      <c r="J18" s="288">
+      <c r="J18" s="286">
         <v>1</v>
       </c>
       <c r="K18" s="250">
@@ -17471,9 +17476,9 @@
         <v>114</v>
       </c>
       <c r="CB18" s="243"/>
-      <c r="CC18" s="289"/>
-      <c r="CD18" s="290"/>
-      <c r="CE18" s="290"/>
+      <c r="CC18" s="287"/>
+      <c r="CD18" s="288"/>
+      <c r="CE18" s="288"/>
       <c r="CF18" s="252"/>
       <c r="CG18" s="252"/>
     </row>
@@ -17508,7 +17513,7 @@
         <f t="shared" si="5"/>
         <v>6400000</v>
       </c>
-      <c r="J19" s="288">
+      <c r="J19" s="286">
         <v>1</v>
       </c>
       <c r="K19" s="250">
@@ -17700,9 +17705,9 @@
         <v>118</v>
       </c>
       <c r="CB19" s="243"/>
-      <c r="CC19" s="289"/>
-      <c r="CD19" s="290"/>
-      <c r="CE19" s="290"/>
+      <c r="CC19" s="287"/>
+      <c r="CD19" s="288"/>
+      <c r="CE19" s="288"/>
       <c r="CF19" s="252"/>
       <c r="CG19" s="252"/>
     </row>
@@ -17737,7 +17742,7 @@
         <f t="shared" si="5"/>
         <v>17810000</v>
       </c>
-      <c r="J20" s="288">
+      <c r="J20" s="286">
         <v>1</v>
       </c>
       <c r="K20" s="250">
@@ -17931,9 +17936,9 @@
         <v>114</v>
       </c>
       <c r="CB20" s="243"/>
-      <c r="CC20" s="289"/>
-      <c r="CD20" s="290"/>
-      <c r="CE20" s="290"/>
+      <c r="CC20" s="287"/>
+      <c r="CD20" s="288"/>
+      <c r="CE20" s="288"/>
       <c r="CF20" s="252"/>
       <c r="CG20" s="252"/>
     </row>
@@ -17968,7 +17973,7 @@
         <f t="shared" si="5"/>
         <v>11210000</v>
       </c>
-      <c r="J21" s="288">
+      <c r="J21" s="286">
         <v>1</v>
       </c>
       <c r="K21" s="250">
@@ -18160,148 +18165,148 @@
         <v>118</v>
       </c>
       <c r="CB21" s="243"/>
-      <c r="CC21" s="289"/>
-      <c r="CD21" s="290"/>
-      <c r="CE21" s="290"/>
+      <c r="CC21" s="287"/>
+      <c r="CD21" s="288"/>
+      <c r="CE21" s="288"/>
       <c r="CF21" s="252"/>
       <c r="CG21" s="252"/>
     </row>
-    <row r="22" spans="1:85" s="291" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B22" s="292"/>
-      <c r="I22" s="293"/>
-      <c r="J22" s="293"/>
-      <c r="K22" s="294"/>
-      <c r="L22" s="294"/>
-      <c r="M22" s="294"/>
-      <c r="N22" s="294"/>
-      <c r="O22" s="294"/>
-      <c r="P22" s="294"/>
-      <c r="Q22" s="294"/>
-      <c r="R22" s="294"/>
-      <c r="S22" s="294"/>
-      <c r="T22" s="294"/>
-      <c r="U22" s="295"/>
-      <c r="V22" s="295"/>
-      <c r="W22" s="296"/>
-      <c r="X22" s="296"/>
-      <c r="AC22" s="297"/>
-      <c r="BJ22" s="298"/>
-      <c r="BN22" s="298"/>
-      <c r="BO22" s="298"/>
-      <c r="BP22" s="298"/>
-      <c r="BQ22" s="298"/>
-      <c r="BR22" s="298"/>
-      <c r="BS22" s="298"/>
-      <c r="BT22" s="298"/>
-      <c r="BU22" s="299"/>
-      <c r="BV22" s="299"/>
-      <c r="BW22" s="299"/>
-      <c r="BX22" s="299"/>
-      <c r="BY22" s="299"/>
-      <c r="CD22" s="300"/>
+    <row r="22" spans="1:85" s="289" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B22" s="290"/>
+      <c r="I22" s="291"/>
+      <c r="J22" s="291"/>
+      <c r="K22" s="292"/>
+      <c r="L22" s="292"/>
+      <c r="M22" s="292"/>
+      <c r="N22" s="292"/>
+      <c r="O22" s="292"/>
+      <c r="P22" s="292"/>
+      <c r="Q22" s="292"/>
+      <c r="R22" s="292"/>
+      <c r="S22" s="292"/>
+      <c r="T22" s="292"/>
+      <c r="U22" s="293"/>
+      <c r="V22" s="293"/>
+      <c r="W22" s="294"/>
+      <c r="X22" s="294"/>
+      <c r="AC22" s="295"/>
+      <c r="BJ22" s="296"/>
+      <c r="BN22" s="296"/>
+      <c r="BO22" s="296"/>
+      <c r="BP22" s="296"/>
+      <c r="BQ22" s="296"/>
+      <c r="BR22" s="296"/>
+      <c r="BS22" s="296"/>
+      <c r="BT22" s="296"/>
+      <c r="BU22" s="297"/>
+      <c r="BV22" s="297"/>
+      <c r="BW22" s="297"/>
+      <c r="BX22" s="297"/>
+      <c r="BY22" s="297"/>
+      <c r="CD22" s="298"/>
     </row>
-    <row r="23" spans="1:85" s="301" customFormat="1" ht="21" customHeight="1">
-      <c r="B23" s="302"/>
-      <c r="C23" s="302"/>
-      <c r="D23" s="302"/>
-      <c r="E23" s="302"/>
-      <c r="F23" s="302"/>
-      <c r="G23" s="302"/>
-      <c r="H23" s="302"/>
-      <c r="I23" s="302"/>
-      <c r="J23" s="303"/>
-      <c r="K23" s="304"/>
-      <c r="L23" s="304"/>
-      <c r="M23" s="304"/>
-      <c r="N23" s="304"/>
-      <c r="O23" s="304"/>
-      <c r="P23" s="304"/>
-      <c r="Q23" s="304"/>
-      <c r="U23" s="305"/>
-      <c r="V23" s="304"/>
-      <c r="W23" s="302"/>
-      <c r="X23" s="302"/>
-      <c r="Y23" s="302"/>
-      <c r="Z23" s="302"/>
-      <c r="AA23" s="302"/>
-      <c r="AB23" s="302"/>
-      <c r="AC23" s="302"/>
-      <c r="AK23" s="302"/>
-      <c r="AM23" s="302"/>
-      <c r="AN23" s="302"/>
-      <c r="AO23" s="302"/>
-      <c r="AP23" s="302"/>
-      <c r="AQ23" s="302"/>
-      <c r="AR23" s="302"/>
-      <c r="AS23" s="302"/>
-      <c r="AT23" s="302"/>
-      <c r="AU23" s="302"/>
-      <c r="AV23" s="302"/>
-      <c r="AW23" s="302"/>
-      <c r="AX23" s="302"/>
-      <c r="BC23" s="306"/>
-      <c r="BD23" s="306"/>
-      <c r="BJ23" s="302"/>
-      <c r="BL23" s="302"/>
-      <c r="BM23" s="302"/>
-      <c r="BN23" s="302" t="s">
+    <row r="23" spans="1:85" s="299" customFormat="1" ht="21" customHeight="1">
+      <c r="B23" s="300"/>
+      <c r="C23" s="300"/>
+      <c r="D23" s="300"/>
+      <c r="E23" s="300"/>
+      <c r="F23" s="300"/>
+      <c r="G23" s="300"/>
+      <c r="H23" s="300"/>
+      <c r="I23" s="300"/>
+      <c r="J23" s="301"/>
+      <c r="K23" s="302"/>
+      <c r="L23" s="302"/>
+      <c r="M23" s="302"/>
+      <c r="N23" s="302"/>
+      <c r="O23" s="302"/>
+      <c r="P23" s="302"/>
+      <c r="Q23" s="302"/>
+      <c r="U23" s="303"/>
+      <c r="V23" s="302"/>
+      <c r="W23" s="300"/>
+      <c r="X23" s="300"/>
+      <c r="Y23" s="300"/>
+      <c r="Z23" s="300"/>
+      <c r="AA23" s="300"/>
+      <c r="AB23" s="300"/>
+      <c r="AC23" s="300"/>
+      <c r="AK23" s="300"/>
+      <c r="AM23" s="300"/>
+      <c r="AN23" s="300"/>
+      <c r="AO23" s="300"/>
+      <c r="AP23" s="300"/>
+      <c r="AQ23" s="300"/>
+      <c r="AR23" s="300"/>
+      <c r="AS23" s="300"/>
+      <c r="AT23" s="300"/>
+      <c r="AU23" s="300"/>
+      <c r="AV23" s="300"/>
+      <c r="AW23" s="300"/>
+      <c r="AX23" s="300"/>
+      <c r="BC23" s="304"/>
+      <c r="BD23" s="304"/>
+      <c r="BJ23" s="300"/>
+      <c r="BL23" s="300"/>
+      <c r="BM23" s="300"/>
+      <c r="BN23" s="300" t="s">
         <v>119</v>
       </c>
-      <c r="BO23" s="302"/>
-      <c r="BP23" s="302"/>
-      <c r="BQ23" s="302"/>
-      <c r="BR23" s="302"/>
-      <c r="BS23" s="302"/>
-      <c r="BT23" s="302"/>
-      <c r="BU23" s="307"/>
-      <c r="BV23" s="307"/>
-      <c r="BW23" s="307"/>
-      <c r="BX23" s="307"/>
-      <c r="BY23" s="307"/>
+      <c r="BO23" s="300"/>
+      <c r="BP23" s="300"/>
+      <c r="BQ23" s="300"/>
+      <c r="BR23" s="300"/>
+      <c r="BS23" s="300"/>
+      <c r="BT23" s="300"/>
+      <c r="BU23" s="305"/>
+      <c r="BV23" s="305"/>
+      <c r="BW23" s="305"/>
+      <c r="BX23" s="305"/>
+      <c r="BY23" s="305"/>
     </row>
-    <row r="24" spans="1:85" s="301" customFormat="1" ht="18" customHeight="1">
-      <c r="B24" s="308"/>
-      <c r="I24" s="303"/>
-      <c r="J24" s="303"/>
-      <c r="K24" s="305"/>
-      <c r="L24" s="305"/>
-      <c r="M24" s="305"/>
-      <c r="N24" s="305"/>
-      <c r="O24" s="305"/>
-      <c r="P24" s="305"/>
-      <c r="Q24" s="305"/>
-      <c r="R24" s="304"/>
-      <c r="U24" s="305"/>
-      <c r="V24" s="305"/>
-      <c r="W24" s="309"/>
-      <c r="X24" s="309"/>
-      <c r="AN24" s="307"/>
-      <c r="AV24" s="302"/>
-      <c r="AW24" s="302"/>
-      <c r="AX24" s="302"/>
-      <c r="AY24" s="307"/>
-      <c r="AZ24" s="307"/>
-      <c r="BA24" s="307"/>
-      <c r="BB24" s="307"/>
-      <c r="BL24" s="302"/>
-      <c r="BM24" s="306"/>
-      <c r="BU24" s="307"/>
-      <c r="BV24" s="307"/>
-      <c r="BW24" s="307"/>
-      <c r="BX24" s="307"/>
-      <c r="BY24" s="307"/>
-      <c r="CD24" s="310"/>
+    <row r="24" spans="1:85" s="299" customFormat="1" ht="18" customHeight="1">
+      <c r="B24" s="306"/>
+      <c r="I24" s="301"/>
+      <c r="J24" s="301"/>
+      <c r="K24" s="303"/>
+      <c r="L24" s="303"/>
+      <c r="M24" s="303"/>
+      <c r="N24" s="303"/>
+      <c r="O24" s="303"/>
+      <c r="P24" s="303"/>
+      <c r="Q24" s="303"/>
+      <c r="R24" s="302"/>
+      <c r="U24" s="303"/>
+      <c r="V24" s="303"/>
+      <c r="W24" s="307"/>
+      <c r="X24" s="307"/>
+      <c r="AN24" s="305"/>
+      <c r="AV24" s="300"/>
+      <c r="AW24" s="300"/>
+      <c r="AX24" s="300"/>
+      <c r="AY24" s="305"/>
+      <c r="AZ24" s="305"/>
+      <c r="BA24" s="305"/>
+      <c r="BB24" s="305"/>
+      <c r="BL24" s="300"/>
+      <c r="BM24" s="304"/>
+      <c r="BU24" s="305"/>
+      <c r="BV24" s="305"/>
+      <c r="BW24" s="305"/>
+      <c r="BX24" s="305"/>
+      <c r="BY24" s="305"/>
+      <c r="CD24" s="308"/>
     </row>
     <row r="25" spans="1:85" ht="15" customHeight="1">
-      <c r="D25" s="314" t="s">
+      <c r="D25" s="312" t="s">
         <v>152</v>
       </c>
-      <c r="I25" s="315"/>
+      <c r="I25" s="313"/>
       <c r="X25" s="258"/>
       <c r="BX25" s="258" t="s">
         <v>147</v>
       </c>
-      <c r="CD25" s="319"/>
+      <c r="CD25" s="317"/>
     </row>
     <row r="26" spans="1:85" ht="73.5" customHeight="1">
       <c r="J26" s="257"/>
@@ -18310,6 +18315,8 @@
   </sheetData>
   <autoFilter ref="A12:CG21" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <mergeCells count="81">
+    <mergeCell ref="AT8:AT11"/>
+    <mergeCell ref="F8:F11"/>
     <mergeCell ref="CB8:CB11"/>
     <mergeCell ref="Y9:Y11"/>
     <mergeCell ref="AA9:AA11"/>
@@ -18318,6 +18325,14 @@
     <mergeCell ref="AX8:AX11"/>
     <mergeCell ref="Y8:AO8"/>
     <mergeCell ref="BJ10:BJ11"/>
+    <mergeCell ref="BZ8:BZ11"/>
+    <mergeCell ref="AJ9:AJ11"/>
+    <mergeCell ref="AL9:AL11"/>
+    <mergeCell ref="AN9:AN11"/>
+    <mergeCell ref="Z9:Z11"/>
+    <mergeCell ref="AD9:AD11"/>
+    <mergeCell ref="AY9:BJ9"/>
+    <mergeCell ref="BT8:BT11"/>
     <mergeCell ref="E8:E11"/>
     <mergeCell ref="G8:G11"/>
     <mergeCell ref="BS8:BS11"/>
@@ -18333,6 +18348,7 @@
     <mergeCell ref="H8:H11"/>
     <mergeCell ref="J8:J11"/>
     <mergeCell ref="V9:W10"/>
+    <mergeCell ref="X9:X11"/>
     <mergeCell ref="BU3:BZ6"/>
     <mergeCell ref="AU8:AU11"/>
     <mergeCell ref="CA8:CA11"/>
@@ -18348,12 +18364,7 @@
     <mergeCell ref="O9:O11"/>
     <mergeCell ref="BH10:BH11"/>
     <mergeCell ref="BQ9:BQ11"/>
-    <mergeCell ref="BT8:BT11"/>
-    <mergeCell ref="F8:F11"/>
-    <mergeCell ref="BZ8:BZ11"/>
-    <mergeCell ref="AJ9:AJ11"/>
-    <mergeCell ref="AL9:AL11"/>
-    <mergeCell ref="AN9:AN11"/>
+    <mergeCell ref="AR8:AR11"/>
     <mergeCell ref="I8:I11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="K8:X8"/>
@@ -18365,6 +18376,11 @@
     <mergeCell ref="AY8:BP8"/>
     <mergeCell ref="AF9:AF11"/>
     <mergeCell ref="AH9:AH11"/>
+    <mergeCell ref="L9:L11"/>
+    <mergeCell ref="N9:N11"/>
+    <mergeCell ref="BG10:BG11"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="AV8:AV11"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="AS8:AS11"/>
     <mergeCell ref="BV8:BY10"/>
@@ -18380,17 +18396,6 @@
     <mergeCell ref="BL10:BL11"/>
     <mergeCell ref="AC9:AC11"/>
     <mergeCell ref="AP8:AP11"/>
-    <mergeCell ref="AR8:AR11"/>
-    <mergeCell ref="L9:L11"/>
-    <mergeCell ref="N9:N11"/>
-    <mergeCell ref="BG10:BG11"/>
-    <mergeCell ref="BI10:BI11"/>
-    <mergeCell ref="X9:X11"/>
-    <mergeCell ref="Z9:Z11"/>
-    <mergeCell ref="AD9:AD11"/>
-    <mergeCell ref="AY9:BJ9"/>
-    <mergeCell ref="AT8:AT11"/>
-    <mergeCell ref="AV8:AV11"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B12 B22:B1048576 C12:BT12">
     <cfRule type="duplicateValues" dxfId="12" priority="96"/>
@@ -18620,87 +18625,87 @@
       <c r="CD2" s="41"/>
     </row>
     <row r="3" spans="1:87" s="43" customFormat="1" ht="11" outlineLevel="1">
-      <c r="A3" s="433"/>
-      <c r="B3" s="421"/>
-      <c r="C3" s="421"/>
-      <c r="D3" s="421"/>
-      <c r="E3" s="421"/>
-      <c r="F3" s="421"/>
-      <c r="G3" s="421"/>
-      <c r="H3" s="421"/>
-      <c r="I3" s="421"/>
-      <c r="J3" s="421"/>
-      <c r="K3" s="421"/>
-      <c r="L3" s="421"/>
-      <c r="M3" s="421"/>
-      <c r="N3" s="421"/>
-      <c r="O3" s="421"/>
-      <c r="P3" s="421"/>
-      <c r="Q3" s="421"/>
-      <c r="R3" s="421"/>
-      <c r="S3" s="421"/>
-      <c r="T3" s="421"/>
-      <c r="U3" s="421"/>
-      <c r="V3" s="421"/>
-      <c r="W3" s="421"/>
-      <c r="X3" s="421"/>
-      <c r="Y3" s="421"/>
-      <c r="Z3" s="421"/>
-      <c r="AA3" s="421"/>
-      <c r="AB3" s="421"/>
-      <c r="AC3" s="421"/>
-      <c r="AD3" s="421"/>
-      <c r="AE3" s="421"/>
-      <c r="AF3" s="421"/>
-      <c r="AG3" s="421"/>
-      <c r="AH3" s="421"/>
-      <c r="AI3" s="421"/>
-      <c r="AJ3" s="421"/>
-      <c r="AK3" s="421"/>
-      <c r="AL3" s="421"/>
-      <c r="AM3" s="421"/>
-      <c r="AN3" s="421"/>
-      <c r="AO3" s="421"/>
-      <c r="AP3" s="421"/>
-      <c r="AQ3" s="421"/>
-      <c r="AR3" s="421"/>
-      <c r="AS3" s="421"/>
-      <c r="AT3" s="421"/>
-      <c r="AU3" s="421"/>
-      <c r="AV3" s="421"/>
-      <c r="AW3" s="421"/>
-      <c r="AX3" s="421"/>
-      <c r="AY3" s="421"/>
-      <c r="AZ3" s="421"/>
-      <c r="BA3" s="421"/>
-      <c r="BB3" s="421"/>
-      <c r="BC3" s="421"/>
-      <c r="BD3" s="421"/>
-      <c r="BE3" s="421"/>
-      <c r="BF3" s="421"/>
-      <c r="BG3" s="421"/>
-      <c r="BH3" s="421"/>
-      <c r="BI3" s="421"/>
-      <c r="BJ3" s="421"/>
-      <c r="BK3" s="421"/>
-      <c r="BL3" s="421"/>
-      <c r="BM3" s="421"/>
-      <c r="BN3" s="421"/>
-      <c r="BO3" s="421"/>
-      <c r="BP3" s="421"/>
-      <c r="BQ3" s="421"/>
-      <c r="BR3" s="421"/>
-      <c r="BS3" s="421"/>
-      <c r="BT3" s="421"/>
-      <c r="BU3" s="421"/>
-      <c r="BW3" s="420" t="s">
+      <c r="A3" s="431"/>
+      <c r="B3" s="419"/>
+      <c r="C3" s="419"/>
+      <c r="D3" s="419"/>
+      <c r="E3" s="419"/>
+      <c r="F3" s="419"/>
+      <c r="G3" s="419"/>
+      <c r="H3" s="419"/>
+      <c r="I3" s="419"/>
+      <c r="J3" s="419"/>
+      <c r="K3" s="419"/>
+      <c r="L3" s="419"/>
+      <c r="M3" s="419"/>
+      <c r="N3" s="419"/>
+      <c r="O3" s="419"/>
+      <c r="P3" s="419"/>
+      <c r="Q3" s="419"/>
+      <c r="R3" s="419"/>
+      <c r="S3" s="419"/>
+      <c r="T3" s="419"/>
+      <c r="U3" s="419"/>
+      <c r="V3" s="419"/>
+      <c r="W3" s="419"/>
+      <c r="X3" s="419"/>
+      <c r="Y3" s="419"/>
+      <c r="Z3" s="419"/>
+      <c r="AA3" s="419"/>
+      <c r="AB3" s="419"/>
+      <c r="AC3" s="419"/>
+      <c r="AD3" s="419"/>
+      <c r="AE3" s="419"/>
+      <c r="AF3" s="419"/>
+      <c r="AG3" s="419"/>
+      <c r="AH3" s="419"/>
+      <c r="AI3" s="419"/>
+      <c r="AJ3" s="419"/>
+      <c r="AK3" s="419"/>
+      <c r="AL3" s="419"/>
+      <c r="AM3" s="419"/>
+      <c r="AN3" s="419"/>
+      <c r="AO3" s="419"/>
+      <c r="AP3" s="419"/>
+      <c r="AQ3" s="419"/>
+      <c r="AR3" s="419"/>
+      <c r="AS3" s="419"/>
+      <c r="AT3" s="419"/>
+      <c r="AU3" s="419"/>
+      <c r="AV3" s="419"/>
+      <c r="AW3" s="419"/>
+      <c r="AX3" s="419"/>
+      <c r="AY3" s="419"/>
+      <c r="AZ3" s="419"/>
+      <c r="BA3" s="419"/>
+      <c r="BB3" s="419"/>
+      <c r="BC3" s="419"/>
+      <c r="BD3" s="419"/>
+      <c r="BE3" s="419"/>
+      <c r="BF3" s="419"/>
+      <c r="BG3" s="419"/>
+      <c r="BH3" s="419"/>
+      <c r="BI3" s="419"/>
+      <c r="BJ3" s="419"/>
+      <c r="BK3" s="419"/>
+      <c r="BL3" s="419"/>
+      <c r="BM3" s="419"/>
+      <c r="BN3" s="419"/>
+      <c r="BO3" s="419"/>
+      <c r="BP3" s="419"/>
+      <c r="BQ3" s="419"/>
+      <c r="BR3" s="419"/>
+      <c r="BS3" s="419"/>
+      <c r="BT3" s="419"/>
+      <c r="BU3" s="419"/>
+      <c r="BW3" s="418" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="421"/>
-      <c r="BY3" s="421"/>
-      <c r="BZ3" s="421"/>
-      <c r="CA3" s="421"/>
-      <c r="CB3" s="421"/>
+      <c r="BX3" s="419"/>
+      <c r="BY3" s="419"/>
+      <c r="BZ3" s="419"/>
+      <c r="CA3" s="419"/>
+      <c r="CB3" s="419"/>
       <c r="CC3" s="42"/>
       <c r="CD3" s="42"/>
       <c r="CE3" s="43" t="s">
@@ -18783,35 +18788,35 @@
       <c r="BS4" s="44"/>
       <c r="BT4" s="44"/>
       <c r="BU4" s="44"/>
-      <c r="BW4" s="421"/>
-      <c r="BX4" s="421"/>
-      <c r="BY4" s="421"/>
-      <c r="BZ4" s="421"/>
-      <c r="CA4" s="421"/>
-      <c r="CB4" s="421"/>
+      <c r="BW4" s="419"/>
+      <c r="BX4" s="419"/>
+      <c r="BY4" s="419"/>
+      <c r="BZ4" s="419"/>
+      <c r="CA4" s="419"/>
+      <c r="CB4" s="419"/>
       <c r="CC4" s="42"/>
       <c r="CD4" s="42"/>
     </row>
     <row r="5" spans="1:87" s="45" customFormat="1">
-      <c r="A5" s="408" t="s">
+      <c r="A5" s="406" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="419" t="s">
+      <c r="B5" s="417" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="407" t="s">
+      <c r="C5" s="405" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="414" t="s">
+      <c r="D5" s="412" t="s">
         <v>141</v>
       </c>
-      <c r="E5" s="414" t="s">
+      <c r="E5" s="412" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="484" t="s">
+      <c r="F5" s="475" t="s">
         <v>142</v>
       </c>
-      <c r="G5" s="407" t="s">
+      <c r="G5" s="405" t="s">
         <v>10</v>
       </c>
       <c r="H5" s="335" t="s">
@@ -18820,186 +18825,186 @@
       <c r="I5" s="335" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="407" t="s">
+      <c r="J5" s="405" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="412" t="s">
+      <c r="K5" s="410" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="404"/>
-      <c r="M5" s="404"/>
-      <c r="N5" s="404"/>
-      <c r="O5" s="404"/>
-      <c r="P5" s="404"/>
-      <c r="Q5" s="404"/>
-      <c r="R5" s="404"/>
-      <c r="S5" s="404"/>
-      <c r="T5" s="404"/>
-      <c r="U5" s="404"/>
-      <c r="V5" s="404"/>
-      <c r="W5" s="404"/>
-      <c r="X5" s="404"/>
-      <c r="Y5" s="407" t="s">
+      <c r="L5" s="402"/>
+      <c r="M5" s="402"/>
+      <c r="N5" s="402"/>
+      <c r="O5" s="402"/>
+      <c r="P5" s="402"/>
+      <c r="Q5" s="402"/>
+      <c r="R5" s="402"/>
+      <c r="S5" s="402"/>
+      <c r="T5" s="402"/>
+      <c r="U5" s="402"/>
+      <c r="V5" s="402"/>
+      <c r="W5" s="402"/>
+      <c r="X5" s="402"/>
+      <c r="Y5" s="405" t="s">
         <v>15</v>
       </c>
-      <c r="Z5" s="404"/>
-      <c r="AA5" s="404"/>
-      <c r="AB5" s="404"/>
-      <c r="AC5" s="404"/>
-      <c r="AD5" s="404"/>
-      <c r="AE5" s="404"/>
-      <c r="AF5" s="404"/>
-      <c r="AG5" s="404"/>
-      <c r="AH5" s="404"/>
-      <c r="AI5" s="404"/>
-      <c r="AJ5" s="404"/>
-      <c r="AK5" s="404"/>
-      <c r="AL5" s="404"/>
-      <c r="AM5" s="404"/>
-      <c r="AN5" s="404"/>
-      <c r="AO5" s="405"/>
-      <c r="AP5" s="407" t="s">
+      <c r="Z5" s="402"/>
+      <c r="AA5" s="402"/>
+      <c r="AB5" s="402"/>
+      <c r="AC5" s="402"/>
+      <c r="AD5" s="402"/>
+      <c r="AE5" s="402"/>
+      <c r="AF5" s="402"/>
+      <c r="AG5" s="402"/>
+      <c r="AH5" s="402"/>
+      <c r="AI5" s="402"/>
+      <c r="AJ5" s="402"/>
+      <c r="AK5" s="402"/>
+      <c r="AL5" s="402"/>
+      <c r="AM5" s="402"/>
+      <c r="AN5" s="402"/>
+      <c r="AO5" s="403"/>
+      <c r="AP5" s="405" t="s">
         <v>16</v>
       </c>
-      <c r="AQ5" s="407" t="s">
+      <c r="AQ5" s="405" t="s">
         <v>17</v>
       </c>
-      <c r="AR5" s="407" t="s">
+      <c r="AR5" s="405" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="407" t="s">
+      <c r="AS5" s="405" t="s">
         <v>19</v>
       </c>
-      <c r="AT5" s="407" t="s">
+      <c r="AT5" s="405" t="s">
         <v>20</v>
       </c>
-      <c r="AU5" s="407" t="s">
+      <c r="AU5" s="405" t="s">
         <v>21</v>
       </c>
-      <c r="AV5" s="407" t="s">
+      <c r="AV5" s="405" t="s">
         <v>22</v>
       </c>
-      <c r="AW5" s="407" t="s">
+      <c r="AW5" s="405" t="s">
         <v>23</v>
       </c>
-      <c r="AX5" s="407" t="s">
+      <c r="AX5" s="405" t="s">
         <v>24</v>
       </c>
-      <c r="AY5" s="403" t="s">
+      <c r="AY5" s="401" t="s">
         <v>25</v>
       </c>
-      <c r="AZ5" s="404"/>
-      <c r="BA5" s="404"/>
-      <c r="BB5" s="404"/>
-      <c r="BC5" s="404"/>
-      <c r="BD5" s="404"/>
-      <c r="BE5" s="404"/>
-      <c r="BF5" s="404"/>
-      <c r="BG5" s="404"/>
-      <c r="BH5" s="404"/>
-      <c r="BI5" s="404"/>
-      <c r="BJ5" s="404"/>
-      <c r="BK5" s="404"/>
-      <c r="BL5" s="404"/>
-      <c r="BM5" s="404"/>
-      <c r="BN5" s="404"/>
-      <c r="BO5" s="404"/>
-      <c r="BP5" s="405"/>
-      <c r="BQ5" s="424" t="s">
+      <c r="AZ5" s="402"/>
+      <c r="BA5" s="402"/>
+      <c r="BB5" s="402"/>
+      <c r="BC5" s="402"/>
+      <c r="BD5" s="402"/>
+      <c r="BE5" s="402"/>
+      <c r="BF5" s="402"/>
+      <c r="BG5" s="402"/>
+      <c r="BH5" s="402"/>
+      <c r="BI5" s="402"/>
+      <c r="BJ5" s="402"/>
+      <c r="BK5" s="402"/>
+      <c r="BL5" s="402"/>
+      <c r="BM5" s="402"/>
+      <c r="BN5" s="402"/>
+      <c r="BO5" s="402"/>
+      <c r="BP5" s="403"/>
+      <c r="BQ5" s="422" t="s">
         <v>26</v>
       </c>
-      <c r="BR5" s="417"/>
-      <c r="BS5" s="403" t="s">
+      <c r="BR5" s="415"/>
+      <c r="BS5" s="401" t="s">
         <v>143</v>
       </c>
-      <c r="BT5" s="403" t="s">
+      <c r="BT5" s="401" t="s">
         <v>27</v>
       </c>
-      <c r="BU5" s="435" t="s">
+      <c r="BU5" s="433" t="s">
         <v>28</v>
       </c>
-      <c r="BW5" s="436" t="s">
+      <c r="BW5" s="434" t="s">
         <v>29</v>
       </c>
-      <c r="BX5" s="425" t="s">
+      <c r="BX5" s="423" t="s">
         <v>30</v>
       </c>
-      <c r="BY5" s="426"/>
-      <c r="BZ5" s="426"/>
-      <c r="CA5" s="417"/>
-      <c r="CB5" s="437" t="s">
+      <c r="BY5" s="424"/>
+      <c r="BZ5" s="424"/>
+      <c r="CA5" s="415"/>
+      <c r="CB5" s="435" t="s">
         <v>31</v>
       </c>
-      <c r="CC5" s="422" t="s">
+      <c r="CC5" s="420" t="s">
         <v>32</v>
       </c>
-      <c r="CD5" s="422" t="s">
+      <c r="CD5" s="420" t="s">
         <v>33</v>
       </c>
       <c r="CH5" s="46"/>
       <c r="CI5" s="47"/>
     </row>
     <row r="6" spans="1:87" s="45" customFormat="1">
-      <c r="A6" s="401"/>
-      <c r="B6" s="401"/>
-      <c r="C6" s="401"/>
-      <c r="D6" s="401"/>
-      <c r="E6" s="401"/>
-      <c r="F6" s="401"/>
-      <c r="G6" s="401"/>
-      <c r="H6" s="401"/>
-      <c r="I6" s="401"/>
-      <c r="J6" s="401"/>
-      <c r="K6" s="415" t="s">
+      <c r="A6" s="399"/>
+      <c r="B6" s="399"/>
+      <c r="C6" s="399"/>
+      <c r="D6" s="399"/>
+      <c r="E6" s="399"/>
+      <c r="F6" s="399"/>
+      <c r="G6" s="399"/>
+      <c r="H6" s="399"/>
+      <c r="I6" s="399"/>
+      <c r="J6" s="399"/>
+      <c r="K6" s="413" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="415" t="s">
+      <c r="L6" s="413" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="415" t="s">
+      <c r="M6" s="413" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="415" t="s">
+      <c r="N6" s="413" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="415" t="s">
+      <c r="O6" s="413" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="415" t="s">
+      <c r="P6" s="413" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="415" t="s">
+      <c r="Q6" s="413" t="s">
         <v>40</v>
       </c>
-      <c r="R6" s="415" t="s">
+      <c r="R6" s="413" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="415" t="s">
+      <c r="S6" s="413" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="415" t="s">
+      <c r="T6" s="413" t="s">
         <v>43</v>
       </c>
-      <c r="U6" s="415" t="s">
+      <c r="U6" s="413" t="s">
         <v>44</v>
       </c>
-      <c r="V6" s="416" t="s">
+      <c r="V6" s="414" t="s">
         <v>45</v>
       </c>
-      <c r="W6" s="417"/>
-      <c r="X6" s="415" t="s">
+      <c r="W6" s="415"/>
+      <c r="X6" s="413" t="s">
         <v>46</v>
       </c>
-      <c r="Y6" s="407" t="s">
+      <c r="Y6" s="405" t="s">
         <v>47</v>
       </c>
-      <c r="Z6" s="407" t="s">
+      <c r="Z6" s="405" t="s">
         <v>48</v>
       </c>
-      <c r="AA6" s="407" t="s">
+      <c r="AA6" s="405" t="s">
         <v>49</v>
       </c>
-      <c r="AB6" s="407" t="s">
+      <c r="AB6" s="405" t="s">
         <v>50</v>
       </c>
       <c r="AC6" s="335" t="s">
@@ -19014,7 +19019,7 @@
       <c r="AF6" s="335" t="s">
         <v>54</v>
       </c>
-      <c r="AG6" s="407" t="s">
+      <c r="AG6" s="405" t="s">
         <v>55</v>
       </c>
       <c r="AH6" s="335" t="s">
@@ -19023,126 +19028,126 @@
       <c r="AI6" s="335" t="s">
         <v>57</v>
       </c>
-      <c r="AJ6" s="407" t="s">
+      <c r="AJ6" s="405" t="s">
         <v>58</v>
       </c>
-      <c r="AK6" s="409" t="s">
+      <c r="AK6" s="407" t="s">
         <v>59</v>
       </c>
-      <c r="AL6" s="407" t="s">
+      <c r="AL6" s="405" t="s">
         <v>60</v>
       </c>
-      <c r="AM6" s="407" t="s">
+      <c r="AM6" s="405" t="s">
         <v>61</v>
       </c>
-      <c r="AN6" s="413" t="s">
+      <c r="AN6" s="411" t="s">
         <v>62</v>
       </c>
-      <c r="AO6" s="407" t="s">
+      <c r="AO6" s="405" t="s">
         <v>63</v>
       </c>
-      <c r="AP6" s="401"/>
-      <c r="AQ6" s="401"/>
-      <c r="AR6" s="401"/>
-      <c r="AS6" s="401"/>
-      <c r="AT6" s="401"/>
-      <c r="AU6" s="401"/>
-      <c r="AV6" s="401"/>
-      <c r="AW6" s="401"/>
-      <c r="AX6" s="401"/>
-      <c r="AY6" s="403" t="s">
+      <c r="AP6" s="399"/>
+      <c r="AQ6" s="399"/>
+      <c r="AR6" s="399"/>
+      <c r="AS6" s="399"/>
+      <c r="AT6" s="399"/>
+      <c r="AU6" s="399"/>
+      <c r="AV6" s="399"/>
+      <c r="AW6" s="399"/>
+      <c r="AX6" s="399"/>
+      <c r="AY6" s="401" t="s">
         <v>25</v>
       </c>
-      <c r="AZ6" s="404"/>
-      <c r="BA6" s="404"/>
-      <c r="BB6" s="404"/>
-      <c r="BC6" s="404"/>
-      <c r="BD6" s="404"/>
-      <c r="BE6" s="404"/>
-      <c r="BF6" s="404"/>
-      <c r="BG6" s="404"/>
-      <c r="BH6" s="404"/>
-      <c r="BI6" s="404"/>
-      <c r="BJ6" s="405"/>
-      <c r="BK6" s="403" t="s">
+      <c r="AZ6" s="402"/>
+      <c r="BA6" s="402"/>
+      <c r="BB6" s="402"/>
+      <c r="BC6" s="402"/>
+      <c r="BD6" s="402"/>
+      <c r="BE6" s="402"/>
+      <c r="BF6" s="402"/>
+      <c r="BG6" s="402"/>
+      <c r="BH6" s="402"/>
+      <c r="BI6" s="402"/>
+      <c r="BJ6" s="403"/>
+      <c r="BK6" s="401" t="s">
         <v>64</v>
       </c>
-      <c r="BL6" s="404"/>
-      <c r="BM6" s="404"/>
-      <c r="BN6" s="404"/>
-      <c r="BO6" s="404"/>
-      <c r="BP6" s="405"/>
-      <c r="BQ6" s="400" t="s">
+      <c r="BL6" s="402"/>
+      <c r="BM6" s="402"/>
+      <c r="BN6" s="402"/>
+      <c r="BO6" s="402"/>
+      <c r="BP6" s="403"/>
+      <c r="BQ6" s="398" t="s">
         <v>65</v>
       </c>
-      <c r="BR6" s="400" t="s">
+      <c r="BR6" s="398" t="s">
         <v>66</v>
       </c>
-      <c r="BS6" s="401"/>
-      <c r="BT6" s="401"/>
-      <c r="BU6" s="410"/>
-      <c r="BW6" s="428"/>
-      <c r="BX6" s="410"/>
-      <c r="BY6" s="427"/>
-      <c r="BZ6" s="427"/>
-      <c r="CA6" s="428"/>
-      <c r="CB6" s="401"/>
-      <c r="CC6" s="401"/>
-      <c r="CD6" s="401"/>
+      <c r="BS6" s="399"/>
+      <c r="BT6" s="399"/>
+      <c r="BU6" s="408"/>
+      <c r="BW6" s="426"/>
+      <c r="BX6" s="408"/>
+      <c r="BY6" s="425"/>
+      <c r="BZ6" s="425"/>
+      <c r="CA6" s="426"/>
+      <c r="CB6" s="399"/>
+      <c r="CC6" s="399"/>
+      <c r="CD6" s="399"/>
       <c r="CH6" s="46"/>
       <c r="CI6" s="47"/>
     </row>
     <row r="7" spans="1:87" s="45" customFormat="1" ht="12">
-      <c r="A7" s="401"/>
-      <c r="B7" s="401"/>
-      <c r="C7" s="401"/>
-      <c r="D7" s="401"/>
-      <c r="E7" s="401"/>
-      <c r="F7" s="401"/>
-      <c r="G7" s="401"/>
-      <c r="H7" s="401"/>
-      <c r="I7" s="401"/>
-      <c r="J7" s="401"/>
-      <c r="K7" s="401"/>
-      <c r="L7" s="401"/>
-      <c r="M7" s="401"/>
-      <c r="N7" s="401"/>
-      <c r="O7" s="401"/>
-      <c r="P7" s="401"/>
-      <c r="Q7" s="401"/>
-      <c r="R7" s="401"/>
-      <c r="S7" s="401"/>
-      <c r="T7" s="401"/>
-      <c r="U7" s="401"/>
-      <c r="V7" s="411"/>
-      <c r="W7" s="418"/>
-      <c r="X7" s="401"/>
-      <c r="Y7" s="401"/>
-      <c r="Z7" s="401"/>
-      <c r="AA7" s="401"/>
-      <c r="AB7" s="401"/>
-      <c r="AC7" s="401"/>
-      <c r="AD7" s="401"/>
-      <c r="AE7" s="401"/>
-      <c r="AF7" s="401"/>
-      <c r="AG7" s="401"/>
-      <c r="AH7" s="401"/>
-      <c r="AI7" s="401"/>
-      <c r="AJ7" s="401"/>
-      <c r="AK7" s="410"/>
-      <c r="AL7" s="401"/>
-      <c r="AM7" s="401"/>
-      <c r="AN7" s="401"/>
-      <c r="AO7" s="401"/>
-      <c r="AP7" s="401"/>
-      <c r="AQ7" s="401"/>
-      <c r="AR7" s="401"/>
-      <c r="AS7" s="401"/>
-      <c r="AT7" s="401"/>
-      <c r="AU7" s="401"/>
-      <c r="AV7" s="401"/>
-      <c r="AW7" s="401"/>
-      <c r="AX7" s="401"/>
+      <c r="A7" s="399"/>
+      <c r="B7" s="399"/>
+      <c r="C7" s="399"/>
+      <c r="D7" s="399"/>
+      <c r="E7" s="399"/>
+      <c r="F7" s="399"/>
+      <c r="G7" s="399"/>
+      <c r="H7" s="399"/>
+      <c r="I7" s="399"/>
+      <c r="J7" s="399"/>
+      <c r="K7" s="399"/>
+      <c r="L7" s="399"/>
+      <c r="M7" s="399"/>
+      <c r="N7" s="399"/>
+      <c r="O7" s="399"/>
+      <c r="P7" s="399"/>
+      <c r="Q7" s="399"/>
+      <c r="R7" s="399"/>
+      <c r="S7" s="399"/>
+      <c r="T7" s="399"/>
+      <c r="U7" s="399"/>
+      <c r="V7" s="409"/>
+      <c r="W7" s="416"/>
+      <c r="X7" s="399"/>
+      <c r="Y7" s="399"/>
+      <c r="Z7" s="399"/>
+      <c r="AA7" s="399"/>
+      <c r="AB7" s="399"/>
+      <c r="AC7" s="399"/>
+      <c r="AD7" s="399"/>
+      <c r="AE7" s="399"/>
+      <c r="AF7" s="399"/>
+      <c r="AG7" s="399"/>
+      <c r="AH7" s="399"/>
+      <c r="AI7" s="399"/>
+      <c r="AJ7" s="399"/>
+      <c r="AK7" s="408"/>
+      <c r="AL7" s="399"/>
+      <c r="AM7" s="399"/>
+      <c r="AN7" s="399"/>
+      <c r="AO7" s="399"/>
+      <c r="AP7" s="399"/>
+      <c r="AQ7" s="399"/>
+      <c r="AR7" s="399"/>
+      <c r="AS7" s="399"/>
+      <c r="AT7" s="399"/>
+      <c r="AU7" s="399"/>
+      <c r="AV7" s="399"/>
+      <c r="AW7" s="399"/>
+      <c r="AX7" s="399"/>
       <c r="AY7" s="29" t="s">
         <v>67</v>
       </c>
@@ -19152,122 +19157,122 @@
       <c r="BA7" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="BB7" s="403" t="s">
+      <c r="BB7" s="401" t="s">
         <v>70</v>
       </c>
-      <c r="BC7" s="406" t="s">
+      <c r="BC7" s="404" t="s">
         <v>71</v>
       </c>
-      <c r="BD7" s="406" t="s">
+      <c r="BD7" s="404" t="s">
         <v>72</v>
       </c>
-      <c r="BE7" s="406" t="s">
+      <c r="BE7" s="404" t="s">
         <v>145</v>
       </c>
-      <c r="BF7" s="406" t="s">
+      <c r="BF7" s="404" t="s">
         <v>74</v>
       </c>
-      <c r="BG7" s="406" t="s">
+      <c r="BG7" s="404" t="s">
         <v>75</v>
       </c>
-      <c r="BH7" s="406" t="s">
+      <c r="BH7" s="404" t="s">
         <v>76</v>
       </c>
-      <c r="BI7" s="406" t="s">
+      <c r="BI7" s="404" t="s">
         <v>79</v>
       </c>
-      <c r="BJ7" s="434" t="s">
+      <c r="BJ7" s="432" t="s">
         <v>80</v>
       </c>
-      <c r="BK7" s="406" t="s">
+      <c r="BK7" s="404" t="s">
         <v>81</v>
       </c>
-      <c r="BL7" s="403" t="s">
+      <c r="BL7" s="401" t="s">
         <v>82</v>
       </c>
-      <c r="BM7" s="406" t="s">
+      <c r="BM7" s="404" t="s">
         <v>83</v>
       </c>
-      <c r="BN7" s="403" t="s">
+      <c r="BN7" s="401" t="s">
         <v>84</v>
       </c>
-      <c r="BO7" s="403" t="s">
+      <c r="BO7" s="401" t="s">
         <v>146</v>
       </c>
-      <c r="BP7" s="403" t="s">
+      <c r="BP7" s="401" t="s">
         <v>85</v>
       </c>
-      <c r="BQ7" s="401"/>
-      <c r="BR7" s="401"/>
-      <c r="BS7" s="401"/>
-      <c r="BT7" s="401"/>
-      <c r="BU7" s="410"/>
-      <c r="BW7" s="428"/>
-      <c r="BX7" s="429"/>
-      <c r="BY7" s="430"/>
-      <c r="BZ7" s="430"/>
-      <c r="CA7" s="431"/>
-      <c r="CB7" s="401"/>
-      <c r="CC7" s="401"/>
-      <c r="CD7" s="401"/>
+      <c r="BQ7" s="399"/>
+      <c r="BR7" s="399"/>
+      <c r="BS7" s="399"/>
+      <c r="BT7" s="399"/>
+      <c r="BU7" s="408"/>
+      <c r="BW7" s="426"/>
+      <c r="BX7" s="427"/>
+      <c r="BY7" s="428"/>
+      <c r="BZ7" s="428"/>
+      <c r="CA7" s="429"/>
+      <c r="CB7" s="399"/>
+      <c r="CC7" s="399"/>
+      <c r="CD7" s="399"/>
       <c r="CH7" s="46"/>
       <c r="CI7" s="47"/>
     </row>
     <row r="8" spans="1:87" s="45" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A8" s="402"/>
-      <c r="B8" s="402"/>
-      <c r="C8" s="402"/>
-      <c r="D8" s="402"/>
-      <c r="E8" s="402"/>
-      <c r="F8" s="402"/>
-      <c r="G8" s="402"/>
-      <c r="H8" s="402"/>
-      <c r="I8" s="402"/>
-      <c r="J8" s="402"/>
-      <c r="K8" s="402"/>
-      <c r="L8" s="402"/>
-      <c r="M8" s="402"/>
-      <c r="N8" s="402"/>
-      <c r="O8" s="402"/>
-      <c r="P8" s="402"/>
-      <c r="Q8" s="402"/>
-      <c r="R8" s="402"/>
-      <c r="S8" s="402"/>
-      <c r="T8" s="402"/>
-      <c r="U8" s="402"/>
+      <c r="A8" s="400"/>
+      <c r="B8" s="400"/>
+      <c r="C8" s="400"/>
+      <c r="D8" s="400"/>
+      <c r="E8" s="400"/>
+      <c r="F8" s="400"/>
+      <c r="G8" s="400"/>
+      <c r="H8" s="400"/>
+      <c r="I8" s="400"/>
+      <c r="J8" s="400"/>
+      <c r="K8" s="400"/>
+      <c r="L8" s="400"/>
+      <c r="M8" s="400"/>
+      <c r="N8" s="400"/>
+      <c r="O8" s="400"/>
+      <c r="P8" s="400"/>
+      <c r="Q8" s="400"/>
+      <c r="R8" s="400"/>
+      <c r="S8" s="400"/>
+      <c r="T8" s="400"/>
+      <c r="U8" s="400"/>
       <c r="V8" s="49" t="s">
         <v>86</v>
       </c>
       <c r="W8" s="49" t="s">
         <v>87</v>
       </c>
-      <c r="X8" s="402"/>
-      <c r="Y8" s="402"/>
-      <c r="Z8" s="402"/>
-      <c r="AA8" s="402"/>
-      <c r="AB8" s="402"/>
-      <c r="AC8" s="402"/>
-      <c r="AD8" s="402"/>
-      <c r="AE8" s="402"/>
-      <c r="AF8" s="402"/>
-      <c r="AG8" s="402"/>
-      <c r="AH8" s="402"/>
-      <c r="AI8" s="402"/>
-      <c r="AJ8" s="402"/>
-      <c r="AK8" s="411"/>
-      <c r="AL8" s="402"/>
-      <c r="AM8" s="402"/>
-      <c r="AN8" s="402"/>
-      <c r="AO8" s="402"/>
-      <c r="AP8" s="402"/>
-      <c r="AQ8" s="402"/>
-      <c r="AR8" s="402"/>
-      <c r="AS8" s="402"/>
-      <c r="AT8" s="402"/>
-      <c r="AU8" s="402"/>
-      <c r="AV8" s="402"/>
-      <c r="AW8" s="402"/>
-      <c r="AX8" s="402"/>
+      <c r="X8" s="400"/>
+      <c r="Y8" s="400"/>
+      <c r="Z8" s="400"/>
+      <c r="AA8" s="400"/>
+      <c r="AB8" s="400"/>
+      <c r="AC8" s="400"/>
+      <c r="AD8" s="400"/>
+      <c r="AE8" s="400"/>
+      <c r="AF8" s="400"/>
+      <c r="AG8" s="400"/>
+      <c r="AH8" s="400"/>
+      <c r="AI8" s="400"/>
+      <c r="AJ8" s="400"/>
+      <c r="AK8" s="409"/>
+      <c r="AL8" s="400"/>
+      <c r="AM8" s="400"/>
+      <c r="AN8" s="400"/>
+      <c r="AO8" s="400"/>
+      <c r="AP8" s="400"/>
+      <c r="AQ8" s="400"/>
+      <c r="AR8" s="400"/>
+      <c r="AS8" s="400"/>
+      <c r="AT8" s="400"/>
+      <c r="AU8" s="400"/>
+      <c r="AV8" s="400"/>
+      <c r="AW8" s="400"/>
+      <c r="AX8" s="400"/>
       <c r="AY8" s="30" t="s">
         <v>88</v>
       </c>
@@ -19277,27 +19282,27 @@
       <c r="BA8" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="BB8" s="402"/>
-      <c r="BC8" s="402"/>
-      <c r="BD8" s="402"/>
-      <c r="BE8" s="402"/>
-      <c r="BF8" s="402"/>
-      <c r="BG8" s="402"/>
-      <c r="BH8" s="402"/>
-      <c r="BI8" s="402"/>
-      <c r="BJ8" s="402"/>
-      <c r="BK8" s="402"/>
-      <c r="BL8" s="402"/>
-      <c r="BM8" s="402"/>
-      <c r="BN8" s="402"/>
-      <c r="BO8" s="402"/>
-      <c r="BP8" s="402"/>
-      <c r="BQ8" s="402"/>
-      <c r="BR8" s="402"/>
-      <c r="BS8" s="402"/>
-      <c r="BT8" s="402"/>
-      <c r="BU8" s="411"/>
-      <c r="BW8" s="431"/>
+      <c r="BB8" s="400"/>
+      <c r="BC8" s="400"/>
+      <c r="BD8" s="400"/>
+      <c r="BE8" s="400"/>
+      <c r="BF8" s="400"/>
+      <c r="BG8" s="400"/>
+      <c r="BH8" s="400"/>
+      <c r="BI8" s="400"/>
+      <c r="BJ8" s="400"/>
+      <c r="BK8" s="400"/>
+      <c r="BL8" s="400"/>
+      <c r="BM8" s="400"/>
+      <c r="BN8" s="400"/>
+      <c r="BO8" s="400"/>
+      <c r="BP8" s="400"/>
+      <c r="BQ8" s="400"/>
+      <c r="BR8" s="400"/>
+      <c r="BS8" s="400"/>
+      <c r="BT8" s="400"/>
+      <c r="BU8" s="409"/>
+      <c r="BW8" s="429"/>
       <c r="BX8" s="23" t="s">
         <v>91</v>
       </c>
@@ -19310,9 +19315,9 @@
       <c r="CA8" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="CB8" s="423"/>
-      <c r="CC8" s="423"/>
-      <c r="CD8" s="423"/>
+      <c r="CB8" s="421"/>
+      <c r="CC8" s="421"/>
+      <c r="CD8" s="421"/>
       <c r="CF8" s="50"/>
       <c r="CH8" s="46"/>
       <c r="CI8" s="47"/>
@@ -21319,8 +21324,6 @@
   </sheetData>
   <autoFilter ref="A9:CI14" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <mergeCells count="82">
-    <mergeCell ref="AU5:AU8"/>
-    <mergeCell ref="AK6:AK8"/>
     <mergeCell ref="A5:A8"/>
     <mergeCell ref="C5:C8"/>
     <mergeCell ref="CD5:CD8"/>
@@ -21340,6 +21343,17 @@
     <mergeCell ref="Q6:Q8"/>
     <mergeCell ref="AC6:AC8"/>
     <mergeCell ref="BW3:CB4"/>
+    <mergeCell ref="X6:X8"/>
+    <mergeCell ref="AV5:AV8"/>
+    <mergeCell ref="AX5:AX8"/>
+    <mergeCell ref="V6:W7"/>
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="AR5:AR8"/>
+    <mergeCell ref="BB7:BB8"/>
+    <mergeCell ref="BD7:BD8"/>
+    <mergeCell ref="AS5:AS8"/>
+    <mergeCell ref="AY6:BJ6"/>
+    <mergeCell ref="BE7:BE8"/>
     <mergeCell ref="CC5:CC8"/>
     <mergeCell ref="H5:H8"/>
     <mergeCell ref="J5:J8"/>
@@ -21356,12 +21370,6 @@
     <mergeCell ref="BC7:BC8"/>
     <mergeCell ref="AE6:AE8"/>
     <mergeCell ref="D5:D8"/>
-    <mergeCell ref="X6:X8"/>
-    <mergeCell ref="AV5:AV8"/>
-    <mergeCell ref="AX5:AX8"/>
-    <mergeCell ref="V6:W7"/>
-    <mergeCell ref="Y6:Y8"/>
-    <mergeCell ref="N6:N8"/>
     <mergeCell ref="F5:F8"/>
     <mergeCell ref="AP5:AP8"/>
     <mergeCell ref="AB6:AB8"/>
@@ -21369,23 +21377,19 @@
     <mergeCell ref="AH6:AH8"/>
     <mergeCell ref="AJ6:AJ8"/>
     <mergeCell ref="T6:T8"/>
-    <mergeCell ref="AR5:AR8"/>
     <mergeCell ref="AA6:AA8"/>
     <mergeCell ref="P6:P8"/>
-    <mergeCell ref="BB7:BB8"/>
-    <mergeCell ref="BD7:BD8"/>
     <mergeCell ref="S6:S8"/>
-    <mergeCell ref="AS5:AS8"/>
     <mergeCell ref="AM6:AM8"/>
     <mergeCell ref="U6:U8"/>
-    <mergeCell ref="AY6:BJ6"/>
     <mergeCell ref="AG6:AG8"/>
-    <mergeCell ref="BE7:BE8"/>
-    <mergeCell ref="BG7:BG8"/>
+    <mergeCell ref="AK6:AK8"/>
     <mergeCell ref="AD6:AD8"/>
     <mergeCell ref="AF6:AF8"/>
     <mergeCell ref="AO6:AO8"/>
     <mergeCell ref="BF7:BF8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="AU5:AU8"/>
     <mergeCell ref="BH7:BH8"/>
     <mergeCell ref="BI7:BI8"/>
     <mergeCell ref="K5:X5"/>
@@ -21401,6 +21405,7 @@
     <mergeCell ref="BQ6:BQ8"/>
     <mergeCell ref="Y5:AO5"/>
     <mergeCell ref="AN6:AN8"/>
+    <mergeCell ref="BG7:BG8"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B9 B12:B16 B20:B1048576 C9:BU9 D10:F10 J10:BI10 BK10:BU10 BW9:CD10">
     <cfRule type="duplicateValues" dxfId="6" priority="68"/>
